--- a/ExcelRAddIn/Tests/Stringfest Examples/R in Excel - Exploratory Data Analysis.xlsx
+++ b/ExcelRAddIn/Tests/Stringfest Examples/R in Excel - Exploratory Data Analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\Stringfest Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E91F411-55FF-45FF-A675-300E52D4DE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74845F48-2525-4D21-AB18-2A29D4126B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{EB0856D8-E191-4F16-B73A-E50C554CDF02}"/>
   </bookViews>
@@ -23,8 +23,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Datasets!$L$3:$L$394</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Histograms!$B$2</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Histograms!$B$2</definedName>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">Datasets!$L$2:$T$394</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -61,7 +59,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Gladstone:</t>
         </r>
@@ -70,7 +68,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Insert the original dataset
@@ -1362,11 +1360,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="174" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1389,19 +1387,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1450,28 +1435,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1527,6 +1510,24 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1537,24 +1538,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2227,7 +2210,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4495800" y="255270"/>
+              <a:off x="6263640" y="255270"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2247,7 +2230,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
+                <a:rPr lang="en-GB" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -2527,18 +2510,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13DC64CD-4B15-405C-BEBC-2233E1694149}" name="tMPG" displayName="tMPG" ref="B2:J400" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13DC64CD-4B15-405C-BEBC-2233E1694149}" name="tMPG" displayName="tMPG" ref="B2:J400" totalsRowShown="0" headerRowDxfId="17">
   <autoFilter ref="B2:J400" xr:uid="{13DC64CD-4B15-405C-BEBC-2233E1694149}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{483D647E-C9BC-48A5-B3F8-94CD3A71F758}" name="mpg" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{55E7DB45-E1A9-4039-A098-A43173200C69}" name="cylinders" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{BE0B9E69-A0AE-49B3-808E-97377F9941AF}" name="displacement" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{D325F481-D6AA-44B5-985F-BEF1C3751FE3}" name="horsepower" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{DE57796C-6328-4043-A031-9FEF21DC18C5}" name="weight" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{AE2DC0B7-33A2-4CF3-8EDD-CEAD933C889F}" name="acceleration" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{E3D48FD3-A8FF-450A-9F5E-CC7A47EAAF51}" name="model_year" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{722899BB-AA86-451B-899B-AA12359DC2AD}" name="origin" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{C98CFA4A-5217-461B-9F6F-5DBF3D9259D7}" name="name" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{483D647E-C9BC-48A5-B3F8-94CD3A71F758}" name="mpg" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{55E7DB45-E1A9-4039-A098-A43173200C69}" name="cylinders" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{BE0B9E69-A0AE-49B3-808E-97377F9941AF}" name="displacement" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{D325F481-D6AA-44B5-985F-BEF1C3751FE3}" name="horsepower" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{DE57796C-6328-4043-A031-9FEF21DC18C5}" name="weight" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{AE2DC0B7-33A2-4CF3-8EDD-CEAD933C889F}" name="acceleration" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{E3D48FD3-A8FF-450A-9F5E-CC7A47EAAF51}" name="model_year" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{722899BB-AA86-451B-899B-AA12359DC2AD}" name="origin" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{C98CFA4A-5217-461B-9F6F-5DBF3D9259D7}" name="name" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2927,6 +2910,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -3111,10 +3095,10 @@
       <c r="R3">
         <v>70</v>
       </c>
-      <c r="S3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T3" s="7" t="s">
+      <c r="S3" t="s">
+        <v>12</v>
+      </c>
+      <c r="T3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3167,10 +3151,10 @@
       <c r="R4">
         <v>70</v>
       </c>
-      <c r="S4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="7" t="s">
+      <c r="S4" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3223,10 +3207,10 @@
       <c r="R5">
         <v>70</v>
       </c>
-      <c r="S5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T5" s="7" t="s">
+      <c r="S5" t="s">
+        <v>12</v>
+      </c>
+      <c r="T5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3279,10 +3263,10 @@
       <c r="R6">
         <v>70</v>
       </c>
-      <c r="S6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T6" s="7" t="s">
+      <c r="S6" t="s">
+        <v>12</v>
+      </c>
+      <c r="T6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3335,10 +3319,10 @@
       <c r="R7">
         <v>70</v>
       </c>
-      <c r="S7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T7" s="7" t="s">
+      <c r="S7" t="s">
+        <v>12</v>
+      </c>
+      <c r="T7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3391,10 +3375,10 @@
       <c r="R8">
         <v>70</v>
       </c>
-      <c r="S8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T8" s="7" t="s">
+      <c r="S8" t="s">
+        <v>12</v>
+      </c>
+      <c r="T8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3447,10 +3431,10 @@
       <c r="R9">
         <v>70</v>
       </c>
-      <c r="S9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T9" s="7" t="s">
+      <c r="S9" t="s">
+        <v>12</v>
+      </c>
+      <c r="T9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3503,10 +3487,10 @@
       <c r="R10">
         <v>70</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T10" s="7" t="s">
+      <c r="S10" t="s">
+        <v>12</v>
+      </c>
+      <c r="T10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3559,10 +3543,10 @@
       <c r="R11">
         <v>70</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T11" s="7" t="s">
+      <c r="S11" t="s">
+        <v>12</v>
+      </c>
+      <c r="T11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3615,10 +3599,10 @@
       <c r="R12">
         <v>70</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T12" s="7" t="s">
+      <c r="S12" t="s">
+        <v>12</v>
+      </c>
+      <c r="T12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3671,10 +3655,10 @@
       <c r="R13">
         <v>70</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T13" s="7" t="s">
+      <c r="S13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3727,10 +3711,10 @@
       <c r="R14">
         <v>70</v>
       </c>
-      <c r="S14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T14" s="7" t="s">
+      <c r="S14" t="s">
+        <v>12</v>
+      </c>
+      <c r="T14" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3783,10 +3767,10 @@
       <c r="R15">
         <v>70</v>
       </c>
-      <c r="S15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T15" s="7" t="s">
+      <c r="S15" t="s">
+        <v>12</v>
+      </c>
+      <c r="T15" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3839,10 +3823,10 @@
       <c r="R16">
         <v>70</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T16" s="7" t="s">
+      <c r="S16" t="s">
+        <v>12</v>
+      </c>
+      <c r="T16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3895,10 +3879,10 @@
       <c r="R17">
         <v>70</v>
       </c>
-      <c r="S17" s="7" t="s">
+      <c r="S17" t="s">
         <v>27</v>
       </c>
-      <c r="T17" s="7" t="s">
+      <c r="T17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3951,10 +3935,10 @@
       <c r="R18">
         <v>70</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T18" s="7" t="s">
+      <c r="S18" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4007,10 +3991,10 @@
       <c r="R19">
         <v>70</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T19" s="7" t="s">
+      <c r="S19" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4063,10 +4047,10 @@
       <c r="R20">
         <v>70</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T20" s="7" t="s">
+      <c r="S20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4119,10 +4103,10 @@
       <c r="R21">
         <v>70</v>
       </c>
-      <c r="S21" s="7" t="s">
+      <c r="S21" t="s">
         <v>27</v>
       </c>
-      <c r="T21" s="7" t="s">
+      <c r="T21" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4175,10 +4159,10 @@
       <c r="R22">
         <v>70</v>
       </c>
-      <c r="S22" s="7" t="s">
+      <c r="S22" t="s">
         <v>33</v>
       </c>
-      <c r="T22" s="7" t="s">
+      <c r="T22" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4231,10 +4215,10 @@
       <c r="R23">
         <v>70</v>
       </c>
-      <c r="S23" s="7" t="s">
+      <c r="S23" t="s">
         <v>33</v>
       </c>
-      <c r="T23" s="7" t="s">
+      <c r="T23" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4287,10 +4271,10 @@
       <c r="R24">
         <v>70</v>
       </c>
-      <c r="S24" s="7" t="s">
+      <c r="S24" t="s">
         <v>33</v>
       </c>
-      <c r="T24" s="7" t="s">
+      <c r="T24" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4343,10 +4327,10 @@
       <c r="R25">
         <v>70</v>
       </c>
-      <c r="S25" s="7" t="s">
+      <c r="S25" t="s">
         <v>33</v>
       </c>
-      <c r="T25" s="7" t="s">
+      <c r="T25" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4399,10 +4383,10 @@
       <c r="R26">
         <v>70</v>
       </c>
-      <c r="S26" s="7" t="s">
+      <c r="S26" t="s">
         <v>33</v>
       </c>
-      <c r="T26" s="7" t="s">
+      <c r="T26" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4455,10 +4439,10 @@
       <c r="R27">
         <v>70</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T27" s="7" t="s">
+      <c r="S27" t="s">
+        <v>12</v>
+      </c>
+      <c r="T27" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4511,10 +4495,10 @@
       <c r="R28">
         <v>70</v>
       </c>
-      <c r="S28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T28" s="7" t="s">
+      <c r="S28" t="s">
+        <v>12</v>
+      </c>
+      <c r="T28" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4567,10 +4551,10 @@
       <c r="R29">
         <v>70</v>
       </c>
-      <c r="S29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T29" s="7" t="s">
+      <c r="S29" t="s">
+        <v>12</v>
+      </c>
+      <c r="T29" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4623,10 +4607,10 @@
       <c r="R30">
         <v>70</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T30" s="7" t="s">
+      <c r="S30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T30" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4679,10 +4663,10 @@
       <c r="R31">
         <v>70</v>
       </c>
-      <c r="S31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T31" s="7" t="s">
+      <c r="S31" t="s">
+        <v>12</v>
+      </c>
+      <c r="T31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4735,10 +4719,10 @@
       <c r="R32">
         <v>71</v>
       </c>
-      <c r="S32" s="7" t="s">
+      <c r="S32" t="s">
         <v>27</v>
       </c>
-      <c r="T32" s="7" t="s">
+      <c r="T32" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4791,10 +4775,10 @@
       <c r="R33">
         <v>71</v>
       </c>
-      <c r="S33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T33" s="7" t="s">
+      <c r="S33" t="s">
+        <v>12</v>
+      </c>
+      <c r="T33" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4847,10 +4831,10 @@
       <c r="R34">
         <v>71</v>
       </c>
-      <c r="S34" s="7" t="s">
+      <c r="S34" t="s">
         <v>27</v>
       </c>
-      <c r="T34" s="7" t="s">
+      <c r="T34" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4901,10 +4885,10 @@
       <c r="R35">
         <v>71</v>
       </c>
-      <c r="S35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T35" s="7" t="s">
+      <c r="S35" t="s">
+        <v>12</v>
+      </c>
+      <c r="T35" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4957,10 +4941,10 @@
       <c r="R36">
         <v>71</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T36" s="7" t="s">
+      <c r="S36" t="s">
+        <v>12</v>
+      </c>
+      <c r="T36" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5013,10 +4997,10 @@
       <c r="R37">
         <v>71</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T37" s="7" t="s">
+      <c r="S37" t="s">
+        <v>12</v>
+      </c>
+      <c r="T37" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5069,10 +5053,10 @@
       <c r="R38">
         <v>71</v>
       </c>
-      <c r="S38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T38" s="7" t="s">
+      <c r="S38" t="s">
+        <v>12</v>
+      </c>
+      <c r="T38" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5125,10 +5109,10 @@
       <c r="R39">
         <v>71</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T39" s="7" t="s">
+      <c r="S39" t="s">
+        <v>12</v>
+      </c>
+      <c r="T39" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5181,10 +5165,10 @@
       <c r="R40">
         <v>71</v>
       </c>
-      <c r="S40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T40" s="7" t="s">
+      <c r="S40" t="s">
+        <v>12</v>
+      </c>
+      <c r="T40" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5237,10 +5221,10 @@
       <c r="R41">
         <v>71</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T41" s="7" t="s">
+      <c r="S41" t="s">
+        <v>12</v>
+      </c>
+      <c r="T41" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5293,10 +5277,10 @@
       <c r="R42">
         <v>71</v>
       </c>
-      <c r="S42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T42" s="7" t="s">
+      <c r="S42" t="s">
+        <v>12</v>
+      </c>
+      <c r="T42" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5349,10 +5333,10 @@
       <c r="R43">
         <v>71</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T43" s="7" t="s">
+      <c r="S43" t="s">
+        <v>12</v>
+      </c>
+      <c r="T43" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5405,10 +5389,10 @@
       <c r="R44">
         <v>71</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T44" s="7" t="s">
+      <c r="S44" t="s">
+        <v>12</v>
+      </c>
+      <c r="T44" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5461,10 +5445,10 @@
       <c r="R45">
         <v>71</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T45" s="7" t="s">
+      <c r="S45" t="s">
+        <v>12</v>
+      </c>
+      <c r="T45" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5517,10 +5501,10 @@
       <c r="R46">
         <v>71</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T46" s="7" t="s">
+      <c r="S46" t="s">
+        <v>12</v>
+      </c>
+      <c r="T46" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5573,10 +5557,10 @@
       <c r="R47">
         <v>71</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T47" s="7" t="s">
+      <c r="S47" t="s">
+        <v>12</v>
+      </c>
+      <c r="T47" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5629,10 +5613,10 @@
       <c r="R48">
         <v>71</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T48" s="7" t="s">
+      <c r="S48" t="s">
+        <v>12</v>
+      </c>
+      <c r="T48" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5685,10 +5669,10 @@
       <c r="R49">
         <v>71</v>
       </c>
-      <c r="S49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T49" s="7" t="s">
+      <c r="S49" t="s">
+        <v>12</v>
+      </c>
+      <c r="T49" t="s">
         <v>56</v>
       </c>
     </row>
@@ -5741,10 +5725,10 @@
       <c r="R50">
         <v>71</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T50" s="7" t="s">
+      <c r="S50" t="s">
+        <v>12</v>
+      </c>
+      <c r="T50" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5797,10 +5781,10 @@
       <c r="R51">
         <v>71</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T51" s="7" t="s">
+      <c r="S51" t="s">
+        <v>12</v>
+      </c>
+      <c r="T51" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5853,10 +5837,10 @@
       <c r="R52">
         <v>71</v>
       </c>
-      <c r="S52" s="7" t="s">
+      <c r="S52" t="s">
         <v>33</v>
       </c>
-      <c r="T52" s="7" t="s">
+      <c r="T52" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5909,10 +5893,10 @@
       <c r="R53">
         <v>71</v>
       </c>
-      <c r="S53" s="7" t="s">
+      <c r="S53" t="s">
         <v>33</v>
       </c>
-      <c r="T53" s="7" t="s">
+      <c r="T53" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5965,10 +5949,10 @@
       <c r="R54">
         <v>71</v>
       </c>
-      <c r="S54" s="7" t="s">
+      <c r="S54" t="s">
         <v>33</v>
       </c>
-      <c r="T54" s="7" t="s">
+      <c r="T54" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6021,10 +6005,10 @@
       <c r="R55">
         <v>71</v>
       </c>
-      <c r="S55" s="7" t="s">
+      <c r="S55" t="s">
         <v>27</v>
       </c>
-      <c r="T55" s="7" t="s">
+      <c r="T55" t="s">
         <v>62</v>
       </c>
     </row>
@@ -6077,10 +6061,10 @@
       <c r="R56">
         <v>71</v>
       </c>
-      <c r="S56" s="7" t="s">
+      <c r="S56" t="s">
         <v>27</v>
       </c>
-      <c r="T56" s="7" t="s">
+      <c r="T56" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6133,10 +6117,10 @@
       <c r="R57">
         <v>71</v>
       </c>
-      <c r="S57" s="7" t="s">
+      <c r="S57" t="s">
         <v>33</v>
       </c>
-      <c r="T57" s="7" t="s">
+      <c r="T57" t="s">
         <v>64</v>
       </c>
     </row>
@@ -6189,10 +6173,10 @@
       <c r="R58">
         <v>71</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T58" s="7" t="s">
+      <c r="S58" t="s">
+        <v>12</v>
+      </c>
+      <c r="T58" t="s">
         <v>65</v>
       </c>
     </row>
@@ -6245,10 +6229,10 @@
       <c r="R59">
         <v>72</v>
       </c>
-      <c r="S59" s="7" t="s">
+      <c r="S59" t="s">
         <v>27</v>
       </c>
-      <c r="T59" s="7" t="s">
+      <c r="T59" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6301,10 +6285,10 @@
       <c r="R60">
         <v>72</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T60" s="7" t="s">
+      <c r="S60" t="s">
+        <v>12</v>
+      </c>
+      <c r="T60" t="s">
         <v>67</v>
       </c>
     </row>
@@ -6357,10 +6341,10 @@
       <c r="R61">
         <v>72</v>
       </c>
-      <c r="S61" s="7" t="s">
+      <c r="S61" t="s">
         <v>33</v>
       </c>
-      <c r="T61" s="7" t="s">
+      <c r="T61" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6413,10 +6397,10 @@
       <c r="R62">
         <v>72</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T62" s="7" t="s">
+      <c r="S62" t="s">
+        <v>12</v>
+      </c>
+      <c r="T62" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6469,10 +6453,10 @@
       <c r="R63">
         <v>72</v>
       </c>
-      <c r="S63" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T63" s="7" t="s">
+      <c r="S63" t="s">
+        <v>12</v>
+      </c>
+      <c r="T63" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6525,10 +6509,10 @@
       <c r="R64">
         <v>72</v>
       </c>
-      <c r="S64" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T64" s="7" t="s">
+      <c r="S64" t="s">
+        <v>12</v>
+      </c>
+      <c r="T64" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6581,10 +6565,10 @@
       <c r="R65">
         <v>72</v>
       </c>
-      <c r="S65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T65" s="7" t="s">
+      <c r="S65" t="s">
+        <v>12</v>
+      </c>
+      <c r="T65" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6637,10 +6621,10 @@
       <c r="R66">
         <v>72</v>
       </c>
-      <c r="S66" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T66" s="7" t="s">
+      <c r="S66" t="s">
+        <v>12</v>
+      </c>
+      <c r="T66" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6693,10 +6677,10 @@
       <c r="R67">
         <v>72</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T67" s="7" t="s">
+      <c r="S67" t="s">
+        <v>12</v>
+      </c>
+      <c r="T67" t="s">
         <v>18</v>
       </c>
     </row>
@@ -6749,10 +6733,10 @@
       <c r="R68">
         <v>72</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T68" s="7" t="s">
+      <c r="S68" t="s">
+        <v>12</v>
+      </c>
+      <c r="T68" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6805,10 +6789,10 @@
       <c r="R69">
         <v>72</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T69" s="7" t="s">
+      <c r="S69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T69" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6861,10 +6845,10 @@
       <c r="R70">
         <v>72</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T70" s="7" t="s">
+      <c r="S70" t="s">
+        <v>12</v>
+      </c>
+      <c r="T70" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6917,10 +6901,10 @@
       <c r="R71">
         <v>72</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T71" s="7" t="s">
+      <c r="S71" t="s">
+        <v>12</v>
+      </c>
+      <c r="T71" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6973,10 +6957,10 @@
       <c r="R72">
         <v>72</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T72" s="7" t="s">
+      <c r="S72" t="s">
+        <v>12</v>
+      </c>
+      <c r="T72" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7029,10 +7013,10 @@
       <c r="R73">
         <v>72</v>
       </c>
-      <c r="S73" s="7" t="s">
+      <c r="S73" t="s">
         <v>27</v>
       </c>
-      <c r="T73" s="7" t="s">
+      <c r="T73" t="s">
         <v>76</v>
       </c>
     </row>
@@ -7085,10 +7069,10 @@
       <c r="R74">
         <v>72</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T74" s="7" t="s">
+      <c r="S74" t="s">
+        <v>12</v>
+      </c>
+      <c r="T74" t="s">
         <v>77</v>
       </c>
     </row>
@@ -7141,10 +7125,10 @@
       <c r="R75">
         <v>72</v>
       </c>
-      <c r="S75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T75" s="7" t="s">
+      <c r="S75" t="s">
+        <v>12</v>
+      </c>
+      <c r="T75" t="s">
         <v>78</v>
       </c>
     </row>
@@ -7197,10 +7181,10 @@
       <c r="R76">
         <v>72</v>
       </c>
-      <c r="S76" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T76" s="7" t="s">
+      <c r="S76" t="s">
+        <v>12</v>
+      </c>
+      <c r="T76" t="s">
         <v>79</v>
       </c>
     </row>
@@ -7253,10 +7237,10 @@
       <c r="R77">
         <v>72</v>
       </c>
-      <c r="S77" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T77" s="7" t="s">
+      <c r="S77" t="s">
+        <v>12</v>
+      </c>
+      <c r="T77" t="s">
         <v>80</v>
       </c>
     </row>
@@ -7309,10 +7293,10 @@
       <c r="R78">
         <v>72</v>
       </c>
-      <c r="S78" s="7" t="s">
+      <c r="S78" t="s">
         <v>33</v>
       </c>
-      <c r="T78" s="7" t="s">
+      <c r="T78" t="s">
         <v>81</v>
       </c>
     </row>
@@ -7365,10 +7349,10 @@
       <c r="R79">
         <v>72</v>
       </c>
-      <c r="S79" s="7" t="s">
+      <c r="S79" t="s">
         <v>33</v>
       </c>
-      <c r="T79" s="7" t="s">
+      <c r="T79" t="s">
         <v>82</v>
       </c>
     </row>
@@ -7421,10 +7405,10 @@
       <c r="R80">
         <v>72</v>
       </c>
-      <c r="S80" s="7" t="s">
+      <c r="S80" t="s">
         <v>33</v>
       </c>
-      <c r="T80" s="7" t="s">
+      <c r="T80" t="s">
         <v>83</v>
       </c>
     </row>
@@ -7477,10 +7461,10 @@
       <c r="R81">
         <v>72</v>
       </c>
-      <c r="S81" s="7" t="s">
+      <c r="S81" t="s">
         <v>33</v>
       </c>
-      <c r="T81" s="7" t="s">
+      <c r="T81" t="s">
         <v>84</v>
       </c>
     </row>
@@ -7533,10 +7517,10 @@
       <c r="R82">
         <v>72</v>
       </c>
-      <c r="S82" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T82" s="7" t="s">
+      <c r="S82" t="s">
+        <v>12</v>
+      </c>
+      <c r="T82" t="s">
         <v>85</v>
       </c>
     </row>
@@ -7589,10 +7573,10 @@
       <c r="R83">
         <v>72</v>
       </c>
-      <c r="S83" s="7" t="s">
+      <c r="S83" t="s">
         <v>27</v>
       </c>
-      <c r="T83" s="7" t="s">
+      <c r="T83" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7645,10 +7629,10 @@
       <c r="R84">
         <v>72</v>
       </c>
-      <c r="S84" s="7" t="s">
+      <c r="S84" t="s">
         <v>27</v>
       </c>
-      <c r="T84" s="7" t="s">
+      <c r="T84" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7701,10 +7685,10 @@
       <c r="R85">
         <v>72</v>
       </c>
-      <c r="S85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T85" s="7" t="s">
+      <c r="S85" t="s">
+        <v>12</v>
+      </c>
+      <c r="T85" t="s">
         <v>88</v>
       </c>
     </row>
@@ -7757,10 +7741,10 @@
       <c r="R86">
         <v>72</v>
       </c>
-      <c r="S86" s="7" t="s">
+      <c r="S86" t="s">
         <v>27</v>
       </c>
-      <c r="T86" s="7" t="s">
+      <c r="T86" t="s">
         <v>89</v>
       </c>
     </row>
@@ -7813,10 +7797,10 @@
       <c r="R87">
         <v>73</v>
       </c>
-      <c r="S87" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T87" s="7" t="s">
+      <c r="S87" t="s">
+        <v>12</v>
+      </c>
+      <c r="T87" t="s">
         <v>90</v>
       </c>
     </row>
@@ -7869,10 +7853,10 @@
       <c r="R88">
         <v>73</v>
       </c>
-      <c r="S88" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T88" s="7" t="s">
+      <c r="S88" t="s">
+        <v>12</v>
+      </c>
+      <c r="T88" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7925,10 +7909,10 @@
       <c r="R89">
         <v>73</v>
       </c>
-      <c r="S89" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T89" s="7" t="s">
+      <c r="S89" t="s">
+        <v>12</v>
+      </c>
+      <c r="T89" t="s">
         <v>91</v>
       </c>
     </row>
@@ -7981,10 +7965,10 @@
       <c r="R90">
         <v>73</v>
       </c>
-      <c r="S90" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T90" s="7" t="s">
+      <c r="S90" t="s">
+        <v>12</v>
+      </c>
+      <c r="T90" t="s">
         <v>92</v>
       </c>
     </row>
@@ -8037,10 +8021,10 @@
       <c r="R91">
         <v>73</v>
       </c>
-      <c r="S91" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T91" s="7" t="s">
+      <c r="S91" t="s">
+        <v>12</v>
+      </c>
+      <c r="T91" t="s">
         <v>93</v>
       </c>
     </row>
@@ -8093,10 +8077,10 @@
       <c r="R92">
         <v>73</v>
       </c>
-      <c r="S92" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T92" s="7" t="s">
+      <c r="S92" t="s">
+        <v>12</v>
+      </c>
+      <c r="T92" t="s">
         <v>94</v>
       </c>
     </row>
@@ -8149,10 +8133,10 @@
       <c r="R93">
         <v>73</v>
       </c>
-      <c r="S93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T93" s="7" t="s">
+      <c r="S93" t="s">
+        <v>12</v>
+      </c>
+      <c r="T93" t="s">
         <v>95</v>
       </c>
     </row>
@@ -8205,10 +8189,10 @@
       <c r="R94">
         <v>73</v>
       </c>
-      <c r="S94" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T94" s="7" t="s">
+      <c r="S94" t="s">
+        <v>12</v>
+      </c>
+      <c r="T94" t="s">
         <v>96</v>
       </c>
     </row>
@@ -8261,10 +8245,10 @@
       <c r="R95">
         <v>73</v>
       </c>
-      <c r="S95" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T95" s="7" t="s">
+      <c r="S95" t="s">
+        <v>12</v>
+      </c>
+      <c r="T95" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8317,10 +8301,10 @@
       <c r="R96">
         <v>73</v>
       </c>
-      <c r="S96" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T96" s="7" t="s">
+      <c r="S96" t="s">
+        <v>12</v>
+      </c>
+      <c r="T96" t="s">
         <v>98</v>
       </c>
     </row>
@@ -8373,10 +8357,10 @@
       <c r="R97">
         <v>73</v>
       </c>
-      <c r="S97" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T97" s="7" t="s">
+      <c r="S97" t="s">
+        <v>12</v>
+      </c>
+      <c r="T97" t="s">
         <v>99</v>
       </c>
     </row>
@@ -8429,10 +8413,10 @@
       <c r="R98">
         <v>73</v>
       </c>
-      <c r="S98" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T98" s="7" t="s">
+      <c r="S98" t="s">
+        <v>12</v>
+      </c>
+      <c r="T98" t="s">
         <v>100</v>
       </c>
     </row>
@@ -8485,10 +8469,10 @@
       <c r="R99">
         <v>73</v>
       </c>
-      <c r="S99" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T99" s="7" t="s">
+      <c r="S99" t="s">
+        <v>12</v>
+      </c>
+      <c r="T99" t="s">
         <v>101</v>
       </c>
     </row>
@@ -8541,10 +8525,10 @@
       <c r="R100">
         <v>73</v>
       </c>
-      <c r="S100" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T100" s="7" t="s">
+      <c r="S100" t="s">
+        <v>12</v>
+      </c>
+      <c r="T100" t="s">
         <v>102</v>
       </c>
     </row>
@@ -8597,10 +8581,10 @@
       <c r="R101">
         <v>73</v>
       </c>
-      <c r="S101" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T101" s="7" t="s">
+      <c r="S101" t="s">
+        <v>12</v>
+      </c>
+      <c r="T101" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8653,10 +8637,10 @@
       <c r="R102">
         <v>73</v>
       </c>
-      <c r="S102" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T102" s="7" t="s">
+      <c r="S102" t="s">
+        <v>12</v>
+      </c>
+      <c r="T102" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8709,10 +8693,10 @@
       <c r="R103">
         <v>73</v>
       </c>
-      <c r="S103" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T103" s="7" t="s">
+      <c r="S103" t="s">
+        <v>12</v>
+      </c>
+      <c r="T103" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8765,10 +8749,10 @@
       <c r="R104">
         <v>73</v>
       </c>
-      <c r="S104" s="7" t="s">
+      <c r="S104" t="s">
         <v>33</v>
       </c>
-      <c r="T104" s="7" t="s">
+      <c r="T104" t="s">
         <v>103</v>
       </c>
     </row>
@@ -8821,10 +8805,10 @@
       <c r="R105">
         <v>73</v>
       </c>
-      <c r="S105" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T105" s="7" t="s">
+      <c r="S105" t="s">
+        <v>12</v>
+      </c>
+      <c r="T105" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8877,10 +8861,10 @@
       <c r="R106">
         <v>73</v>
       </c>
-      <c r="S106" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T106" s="7" t="s">
+      <c r="S106" t="s">
+        <v>12</v>
+      </c>
+      <c r="T106" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8933,10 +8917,10 @@
       <c r="R107">
         <v>73</v>
       </c>
-      <c r="S107" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T107" s="7" t="s">
+      <c r="S107" t="s">
+        <v>12</v>
+      </c>
+      <c r="T107" t="s">
         <v>105</v>
       </c>
     </row>
@@ -8989,10 +8973,10 @@
       <c r="R108">
         <v>73</v>
       </c>
-      <c r="S108" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T108" s="7" t="s">
+      <c r="S108" t="s">
+        <v>12</v>
+      </c>
+      <c r="T108" t="s">
         <v>106</v>
       </c>
     </row>
@@ -9045,10 +9029,10 @@
       <c r="R109">
         <v>73</v>
       </c>
-      <c r="S109" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T109" s="7" t="s">
+      <c r="S109" t="s">
+        <v>12</v>
+      </c>
+      <c r="T109" t="s">
         <v>39</v>
       </c>
     </row>
@@ -9101,10 +9085,10 @@
       <c r="R110">
         <v>73</v>
       </c>
-      <c r="S110" s="7" t="s">
+      <c r="S110" t="s">
         <v>27</v>
       </c>
-      <c r="T110" s="7" t="s">
+      <c r="T110" t="s">
         <v>107</v>
       </c>
     </row>
@@ -9157,10 +9141,10 @@
       <c r="R111">
         <v>73</v>
       </c>
-      <c r="S111" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T111" s="7" t="s">
+      <c r="S111" t="s">
+        <v>12</v>
+      </c>
+      <c r="T111" t="s">
         <v>69</v>
       </c>
     </row>
@@ -9213,10 +9197,10 @@
       <c r="R112">
         <v>73</v>
       </c>
-      <c r="S112" s="7" t="s">
+      <c r="S112" t="s">
         <v>27</v>
       </c>
-      <c r="T112" s="7" t="s">
+      <c r="T112" t="s">
         <v>108</v>
       </c>
     </row>
@@ -9269,10 +9253,10 @@
       <c r="R113">
         <v>73</v>
       </c>
-      <c r="S113" s="7" t="s">
+      <c r="S113" t="s">
         <v>27</v>
       </c>
-      <c r="T113" s="7" t="s">
+      <c r="T113" t="s">
         <v>109</v>
       </c>
     </row>
@@ -9325,10 +9309,10 @@
       <c r="R114">
         <v>73</v>
       </c>
-      <c r="S114" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T114" s="7" t="s">
+      <c r="S114" t="s">
+        <v>12</v>
+      </c>
+      <c r="T114" t="s">
         <v>46</v>
       </c>
     </row>
@@ -9381,10 +9365,10 @@
       <c r="R115">
         <v>73</v>
       </c>
-      <c r="S115" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T115" s="7" t="s">
+      <c r="S115" t="s">
+        <v>12</v>
+      </c>
+      <c r="T115" t="s">
         <v>110</v>
       </c>
     </row>
@@ -9437,10 +9421,10 @@
       <c r="R116">
         <v>73</v>
       </c>
-      <c r="S116" s="7" t="s">
+      <c r="S116" t="s">
         <v>33</v>
       </c>
-      <c r="T116" s="7" t="s">
+      <c r="T116" t="s">
         <v>111</v>
       </c>
     </row>
@@ -9493,10 +9477,10 @@
       <c r="R117">
         <v>73</v>
       </c>
-      <c r="S117" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T117" s="7" t="s">
+      <c r="S117" t="s">
+        <v>12</v>
+      </c>
+      <c r="T117" t="s">
         <v>112</v>
       </c>
     </row>
@@ -9549,10 +9533,10 @@
       <c r="R118">
         <v>73</v>
       </c>
-      <c r="S118" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T118" s="7" t="s">
+      <c r="S118" t="s">
+        <v>12</v>
+      </c>
+      <c r="T118" t="s">
         <v>113</v>
       </c>
     </row>
@@ -9605,10 +9589,10 @@
       <c r="R119">
         <v>73</v>
       </c>
-      <c r="S119" s="7" t="s">
+      <c r="S119" t="s">
         <v>33</v>
       </c>
-      <c r="T119" s="7" t="s">
+      <c r="T119" t="s">
         <v>114</v>
       </c>
     </row>
@@ -9661,10 +9645,10 @@
       <c r="R120">
         <v>73</v>
       </c>
-      <c r="S120" s="7" t="s">
+      <c r="S120" t="s">
         <v>33</v>
       </c>
-      <c r="T120" s="7" t="s">
+      <c r="T120" t="s">
         <v>115</v>
       </c>
     </row>
@@ -9717,10 +9701,10 @@
       <c r="R121">
         <v>73</v>
       </c>
-      <c r="S121" s="7" t="s">
+      <c r="S121" t="s">
         <v>33</v>
       </c>
-      <c r="T121" s="7" t="s">
+      <c r="T121" t="s">
         <v>116</v>
       </c>
     </row>
@@ -9773,10 +9757,10 @@
       <c r="R122">
         <v>73</v>
       </c>
-      <c r="S122" s="7" t="s">
+      <c r="S122" t="s">
         <v>33</v>
       </c>
-      <c r="T122" s="7" t="s">
+      <c r="T122" t="s">
         <v>117</v>
       </c>
     </row>
@@ -9829,10 +9813,10 @@
       <c r="R123">
         <v>73</v>
       </c>
-      <c r="S123" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T123" s="7" t="s">
+      <c r="S123" t="s">
+        <v>12</v>
+      </c>
+      <c r="T123" t="s">
         <v>118</v>
       </c>
     </row>
@@ -9885,10 +9869,10 @@
       <c r="R124">
         <v>73</v>
       </c>
-      <c r="S124" s="7" t="s">
+      <c r="S124" t="s">
         <v>33</v>
       </c>
-      <c r="T124" s="7" t="s">
+      <c r="T124" t="s">
         <v>119</v>
       </c>
     </row>
@@ -9941,10 +9925,10 @@
       <c r="R125">
         <v>73</v>
       </c>
-      <c r="S125" s="7" t="s">
+      <c r="S125" t="s">
         <v>27</v>
       </c>
-      <c r="T125" s="7" t="s">
+      <c r="T125" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9997,10 +9981,10 @@
       <c r="R126">
         <v>73</v>
       </c>
-      <c r="S126" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T126" s="7" t="s">
+      <c r="S126" t="s">
+        <v>12</v>
+      </c>
+      <c r="T126" t="s">
         <v>121</v>
       </c>
     </row>
@@ -10053,10 +10037,10 @@
       <c r="R127">
         <v>74</v>
       </c>
-      <c r="S127" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T127" s="7" t="s">
+      <c r="S127" t="s">
+        <v>12</v>
+      </c>
+      <c r="T127" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10109,10 +10093,10 @@
       <c r="R128">
         <v>74</v>
       </c>
-      <c r="S128" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T128" s="7" t="s">
+      <c r="S128" t="s">
+        <v>12</v>
+      </c>
+      <c r="T128" t="s">
         <v>30</v>
       </c>
     </row>
@@ -10163,10 +10147,10 @@
       <c r="R129">
         <v>74</v>
       </c>
-      <c r="S129" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T129" s="7" t="s">
+      <c r="S129" t="s">
+        <v>12</v>
+      </c>
+      <c r="T129" t="s">
         <v>122</v>
       </c>
     </row>
@@ -10219,10 +10203,10 @@
       <c r="R130">
         <v>74</v>
       </c>
-      <c r="S130" s="7" t="s">
+      <c r="S130" t="s">
         <v>27</v>
       </c>
-      <c r="T130" s="7" t="s">
+      <c r="T130" t="s">
         <v>123</v>
       </c>
     </row>
@@ -10275,10 +10259,10 @@
       <c r="R131">
         <v>74</v>
       </c>
-      <c r="S131" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T131" s="7" t="s">
+      <c r="S131" t="s">
+        <v>12</v>
+      </c>
+      <c r="T131" t="s">
         <v>46</v>
       </c>
     </row>
@@ -10331,10 +10315,10 @@
       <c r="R132">
         <v>74</v>
       </c>
-      <c r="S132" s="7" t="s">
+      <c r="S132" t="s">
         <v>27</v>
       </c>
-      <c r="T132" s="7" t="s">
+      <c r="T132" t="s">
         <v>62</v>
       </c>
     </row>
@@ -10387,10 +10371,10 @@
       <c r="R133">
         <v>74</v>
       </c>
-      <c r="S133" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T133" s="7" t="s">
+      <c r="S133" t="s">
+        <v>12</v>
+      </c>
+      <c r="T133" t="s">
         <v>69</v>
       </c>
     </row>
@@ -10443,10 +10427,10 @@
       <c r="R134">
         <v>74</v>
       </c>
-      <c r="S134" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T134" s="7" t="s">
+      <c r="S134" t="s">
+        <v>12</v>
+      </c>
+      <c r="T134" t="s">
         <v>124</v>
       </c>
     </row>
@@ -10499,10 +10483,10 @@
       <c r="R135">
         <v>74</v>
       </c>
-      <c r="S135" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T135" s="7" t="s">
+      <c r="S135" t="s">
+        <v>12</v>
+      </c>
+      <c r="T135" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10555,10 +10539,10 @@
       <c r="R136">
         <v>74</v>
       </c>
-      <c r="S136" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T136" s="7" t="s">
+      <c r="S136" t="s">
+        <v>12</v>
+      </c>
+      <c r="T136" t="s">
         <v>125</v>
       </c>
     </row>
@@ -10611,10 +10595,10 @@
       <c r="R137">
         <v>74</v>
       </c>
-      <c r="S137" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T137" s="7" t="s">
+      <c r="S137" t="s">
+        <v>12</v>
+      </c>
+      <c r="T137" t="s">
         <v>92</v>
       </c>
     </row>
@@ -10667,10 +10651,10 @@
       <c r="R138">
         <v>74</v>
       </c>
-      <c r="S138" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T138" s="7" t="s">
+      <c r="S138" t="s">
+        <v>12</v>
+      </c>
+      <c r="T138" t="s">
         <v>126</v>
       </c>
     </row>
@@ -10723,10 +10707,10 @@
       <c r="R139">
         <v>74</v>
       </c>
-      <c r="S139" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T139" s="7" t="s">
+      <c r="S139" t="s">
+        <v>12</v>
+      </c>
+      <c r="T139" t="s">
         <v>127</v>
       </c>
     </row>
@@ -10779,10 +10763,10 @@
       <c r="R140">
         <v>74</v>
       </c>
-      <c r="S140" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T140" s="7" t="s">
+      <c r="S140" t="s">
+        <v>12</v>
+      </c>
+      <c r="T140" t="s">
         <v>79</v>
       </c>
     </row>
@@ -10835,10 +10819,10 @@
       <c r="R141">
         <v>74</v>
       </c>
-      <c r="S141" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T141" s="7" t="s">
+      <c r="S141" t="s">
+        <v>12</v>
+      </c>
+      <c r="T141" t="s">
         <v>77</v>
       </c>
     </row>
@@ -10891,10 +10875,10 @@
       <c r="R142">
         <v>74</v>
       </c>
-      <c r="S142" s="7" t="s">
+      <c r="S142" t="s">
         <v>33</v>
       </c>
-      <c r="T142" s="7" t="s">
+      <c r="T142" t="s">
         <v>128</v>
       </c>
     </row>
@@ -10947,10 +10931,10 @@
       <c r="R143">
         <v>74</v>
       </c>
-      <c r="S143" s="7" t="s">
+      <c r="S143" t="s">
         <v>33</v>
       </c>
-      <c r="T143" s="7" t="s">
+      <c r="T143" t="s">
         <v>129</v>
       </c>
     </row>
@@ -11003,10 +10987,10 @@
       <c r="R144">
         <v>74</v>
       </c>
-      <c r="S144" s="7" t="s">
+      <c r="S144" t="s">
         <v>33</v>
       </c>
-      <c r="T144" s="7" t="s">
+      <c r="T144" t="s">
         <v>115</v>
       </c>
     </row>
@@ -11059,10 +11043,10 @@
       <c r="R145">
         <v>74</v>
       </c>
-      <c r="S145" s="7" t="s">
+      <c r="S145" t="s">
         <v>27</v>
       </c>
-      <c r="T145" s="7" t="s">
+      <c r="T145" t="s">
         <v>45</v>
       </c>
     </row>
@@ -11115,10 +11099,10 @@
       <c r="R146">
         <v>74</v>
       </c>
-      <c r="S146" s="7" t="s">
+      <c r="S146" t="s">
         <v>27</v>
       </c>
-      <c r="T146" s="7" t="s">
+      <c r="T146" t="s">
         <v>130</v>
       </c>
     </row>
@@ -11171,10 +11155,10 @@
       <c r="R147">
         <v>74</v>
       </c>
-      <c r="S147" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T147" s="7" t="s">
+      <c r="S147" t="s">
+        <v>12</v>
+      </c>
+      <c r="T147" t="s">
         <v>131</v>
       </c>
     </row>
@@ -11227,10 +11211,10 @@
       <c r="R148">
         <v>74</v>
       </c>
-      <c r="S148" s="7" t="s">
+      <c r="S148" t="s">
         <v>33</v>
       </c>
-      <c r="T148" s="7" t="s">
+      <c r="T148" t="s">
         <v>114</v>
       </c>
     </row>
@@ -11283,10 +11267,10 @@
       <c r="R149">
         <v>74</v>
       </c>
-      <c r="S149" s="7" t="s">
+      <c r="S149" t="s">
         <v>33</v>
       </c>
-      <c r="T149" s="7" t="s">
+      <c r="T149" t="s">
         <v>132</v>
       </c>
     </row>
@@ -11339,10 +11323,10 @@
       <c r="R150">
         <v>74</v>
       </c>
-      <c r="S150" s="7" t="s">
+      <c r="S150" t="s">
         <v>27</v>
       </c>
-      <c r="T150" s="7" t="s">
+      <c r="T150" t="s">
         <v>133</v>
       </c>
     </row>
@@ -11395,10 +11379,10 @@
       <c r="R151">
         <v>74</v>
       </c>
-      <c r="S151" s="7" t="s">
+      <c r="S151" t="s">
         <v>27</v>
       </c>
-      <c r="T151" s="7" t="s">
+      <c r="T151" t="s">
         <v>134</v>
       </c>
     </row>
@@ -11451,10 +11435,10 @@
       <c r="R152">
         <v>74</v>
       </c>
-      <c r="S152" s="7" t="s">
+      <c r="S152" t="s">
         <v>33</v>
       </c>
-      <c r="T152" s="7" t="s">
+      <c r="T152" t="s">
         <v>135</v>
       </c>
     </row>
@@ -11507,10 +11491,10 @@
       <c r="R153">
         <v>75</v>
       </c>
-      <c r="S153" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T153" s="7" t="s">
+      <c r="S153" t="s">
+        <v>12</v>
+      </c>
+      <c r="T153" t="s">
         <v>136</v>
       </c>
     </row>
@@ -11563,10 +11547,10 @@
       <c r="R154">
         <v>75</v>
       </c>
-      <c r="S154" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T154" s="7" t="s">
+      <c r="S154" t="s">
+        <v>12</v>
+      </c>
+      <c r="T154" t="s">
         <v>122</v>
       </c>
     </row>
@@ -11619,10 +11603,10 @@
       <c r="R155">
         <v>75</v>
       </c>
-      <c r="S155" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T155" s="7" t="s">
+      <c r="S155" t="s">
+        <v>12</v>
+      </c>
+      <c r="T155" t="s">
         <v>137</v>
       </c>
     </row>
@@ -11675,10 +11659,10 @@
       <c r="R156">
         <v>75</v>
       </c>
-      <c r="S156" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T156" s="7" t="s">
+      <c r="S156" t="s">
+        <v>12</v>
+      </c>
+      <c r="T156" t="s">
         <v>31</v>
       </c>
     </row>
@@ -11731,10 +11715,10 @@
       <c r="R157">
         <v>75</v>
       </c>
-      <c r="S157" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T157" s="7" t="s">
+      <c r="S157" t="s">
+        <v>12</v>
+      </c>
+      <c r="T157" t="s">
         <v>21</v>
       </c>
     </row>
@@ -11787,10 +11771,10 @@
       <c r="R158">
         <v>75</v>
       </c>
-      <c r="S158" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T158" s="7" t="s">
+      <c r="S158" t="s">
+        <v>12</v>
+      </c>
+      <c r="T158" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11843,10 +11827,10 @@
       <c r="R159">
         <v>75</v>
       </c>
-      <c r="S159" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T159" s="7" t="s">
+      <c r="S159" t="s">
+        <v>12</v>
+      </c>
+      <c r="T159" t="s">
         <v>139</v>
       </c>
     </row>
@@ -11899,10 +11883,10 @@
       <c r="R160">
         <v>75</v>
       </c>
-      <c r="S160" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T160" s="7" t="s">
+      <c r="S160" t="s">
+        <v>12</v>
+      </c>
+      <c r="T160" t="s">
         <v>96</v>
       </c>
     </row>
@@ -11955,10 +11939,10 @@
       <c r="R161">
         <v>75</v>
       </c>
-      <c r="S161" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T161" s="7" t="s">
+      <c r="S161" t="s">
+        <v>12</v>
+      </c>
+      <c r="T161" t="s">
         <v>140</v>
       </c>
     </row>
@@ -12011,10 +11995,10 @@
       <c r="R162">
         <v>75</v>
       </c>
-      <c r="S162" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T162" s="7" t="s">
+      <c r="S162" t="s">
+        <v>12</v>
+      </c>
+      <c r="T162" t="s">
         <v>141</v>
       </c>
     </row>
@@ -12067,10 +12051,10 @@
       <c r="R163">
         <v>75</v>
       </c>
-      <c r="S163" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T163" s="7" t="s">
+      <c r="S163" t="s">
+        <v>12</v>
+      </c>
+      <c r="T163" t="s">
         <v>49</v>
       </c>
     </row>
@@ -12123,10 +12107,10 @@
       <c r="R164">
         <v>75</v>
       </c>
-      <c r="S164" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T164" s="7" t="s">
+      <c r="S164" t="s">
+        <v>12</v>
+      </c>
+      <c r="T164" t="s">
         <v>142</v>
       </c>
     </row>
@@ -12179,10 +12163,10 @@
       <c r="R165">
         <v>75</v>
       </c>
-      <c r="S165" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T165" s="7" t="s">
+      <c r="S165" t="s">
+        <v>12</v>
+      </c>
+      <c r="T165" t="s">
         <v>143</v>
       </c>
     </row>
@@ -12235,10 +12219,10 @@
       <c r="R166">
         <v>75</v>
       </c>
-      <c r="S166" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T166" s="7" t="s">
+      <c r="S166" t="s">
+        <v>12</v>
+      </c>
+      <c r="T166" t="s">
         <v>144</v>
       </c>
     </row>
@@ -12291,10 +12275,10 @@
       <c r="R167">
         <v>75</v>
       </c>
-      <c r="S167" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T167" s="7" t="s">
+      <c r="S167" t="s">
+        <v>12</v>
+      </c>
+      <c r="T167" t="s">
         <v>145</v>
       </c>
     </row>
@@ -12347,10 +12331,10 @@
       <c r="R168">
         <v>75</v>
       </c>
-      <c r="S168" s="7" t="s">
+      <c r="S168" t="s">
         <v>27</v>
       </c>
-      <c r="T168" s="7" t="s">
+      <c r="T168" t="s">
         <v>146</v>
       </c>
     </row>
@@ -12403,10 +12387,10 @@
       <c r="R169">
         <v>75</v>
       </c>
-      <c r="S169" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T169" s="7" t="s">
+      <c r="S169" t="s">
+        <v>12</v>
+      </c>
+      <c r="T169" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12459,10 +12443,10 @@
       <c r="R170">
         <v>75</v>
       </c>
-      <c r="S170" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T170" s="7" t="s">
+      <c r="S170" t="s">
+        <v>12</v>
+      </c>
+      <c r="T170" t="s">
         <v>39</v>
       </c>
     </row>
@@ -12515,10 +12499,10 @@
       <c r="R171">
         <v>75</v>
       </c>
-      <c r="S171" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T171" s="7" t="s">
+      <c r="S171" t="s">
+        <v>12</v>
+      </c>
+      <c r="T171" t="s">
         <v>147</v>
       </c>
     </row>
@@ -12571,10 +12555,10 @@
       <c r="R172">
         <v>75</v>
       </c>
-      <c r="S172" s="7" t="s">
+      <c r="S172" t="s">
         <v>27</v>
       </c>
-      <c r="T172" s="7" t="s">
+      <c r="T172" t="s">
         <v>45</v>
       </c>
     </row>
@@ -12627,10 +12611,10 @@
       <c r="R173">
         <v>75</v>
       </c>
-      <c r="S173" s="7" t="s">
+      <c r="S173" t="s">
         <v>33</v>
       </c>
-      <c r="T173" s="7" t="s">
+      <c r="T173" t="s">
         <v>129</v>
       </c>
     </row>
@@ -12683,10 +12667,10 @@
       <c r="R174">
         <v>75</v>
       </c>
-      <c r="S174" s="7" t="s">
+      <c r="S174" t="s">
         <v>27</v>
       </c>
-      <c r="T174" s="7" t="s">
+      <c r="T174" t="s">
         <v>130</v>
       </c>
     </row>
@@ -12739,10 +12723,10 @@
       <c r="R175">
         <v>75</v>
       </c>
-      <c r="S175" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T175" s="7" t="s">
+      <c r="S175" t="s">
+        <v>12</v>
+      </c>
+      <c r="T175" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12795,10 +12779,10 @@
       <c r="R176">
         <v>75</v>
       </c>
-      <c r="S176" s="7" t="s">
+      <c r="S176" t="s">
         <v>33</v>
       </c>
-      <c r="T176" s="7" t="s">
+      <c r="T176" t="s">
         <v>148</v>
       </c>
     </row>
@@ -12851,10 +12835,10 @@
       <c r="R177">
         <v>75</v>
       </c>
-      <c r="S177" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T177" s="7" t="s">
+      <c r="S177" t="s">
+        <v>12</v>
+      </c>
+      <c r="T177" t="s">
         <v>149</v>
       </c>
     </row>
@@ -12907,10 +12891,10 @@
       <c r="R178">
         <v>75</v>
       </c>
-      <c r="S178" s="7" t="s">
+      <c r="S178" t="s">
         <v>33</v>
       </c>
-      <c r="T178" s="7" t="s">
+      <c r="T178" t="s">
         <v>116</v>
       </c>
     </row>
@@ -12963,10 +12947,10 @@
       <c r="R179">
         <v>75</v>
       </c>
-      <c r="S179" s="7" t="s">
+      <c r="S179" t="s">
         <v>33</v>
       </c>
-      <c r="T179" s="7" t="s">
+      <c r="T179" t="s">
         <v>35</v>
       </c>
     </row>
@@ -13019,10 +13003,10 @@
       <c r="R180">
         <v>75</v>
       </c>
-      <c r="S180" s="7" t="s">
+      <c r="S180" t="s">
         <v>33</v>
       </c>
-      <c r="T180" s="7" t="s">
+      <c r="T180" t="s">
         <v>150</v>
       </c>
     </row>
@@ -13075,10 +13059,10 @@
       <c r="R181">
         <v>75</v>
       </c>
-      <c r="S181" s="7" t="s">
+      <c r="S181" t="s">
         <v>33</v>
       </c>
-      <c r="T181" s="7" t="s">
+      <c r="T181" t="s">
         <v>119</v>
       </c>
     </row>
@@ -13131,10 +13115,10 @@
       <c r="R182">
         <v>75</v>
       </c>
-      <c r="S182" s="7" t="s">
+      <c r="S182" t="s">
         <v>27</v>
       </c>
-      <c r="T182" s="7" t="s">
+      <c r="T182" t="s">
         <v>151</v>
       </c>
     </row>
@@ -13187,10 +13171,10 @@
       <c r="R183">
         <v>76</v>
       </c>
-      <c r="S183" s="7" t="s">
+      <c r="S183" t="s">
         <v>33</v>
       </c>
-      <c r="T183" s="7" t="s">
+      <c r="T183" t="s">
         <v>152</v>
       </c>
     </row>
@@ -13243,10 +13227,10 @@
       <c r="R184">
         <v>76</v>
       </c>
-      <c r="S184" s="7" t="s">
+      <c r="S184" t="s">
         <v>33</v>
       </c>
-      <c r="T184" s="7" t="s">
+      <c r="T184" t="s">
         <v>59</v>
       </c>
     </row>
@@ -13299,10 +13283,10 @@
       <c r="R185">
         <v>76</v>
       </c>
-      <c r="S185" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T185" s="7" t="s">
+      <c r="S185" t="s">
+        <v>12</v>
+      </c>
+      <c r="T185" t="s">
         <v>153</v>
       </c>
     </row>
@@ -13355,10 +13339,10 @@
       <c r="R186">
         <v>76</v>
       </c>
-      <c r="S186" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T186" s="7" t="s">
+      <c r="S186" t="s">
+        <v>12</v>
+      </c>
+      <c r="T186" t="s">
         <v>131</v>
       </c>
     </row>
@@ -13411,10 +13395,10 @@
       <c r="R187">
         <v>76</v>
       </c>
-      <c r="S187" s="7" t="s">
+      <c r="S187" t="s">
         <v>33</v>
       </c>
-      <c r="T187" s="7" t="s">
+      <c r="T187" t="s">
         <v>154</v>
       </c>
     </row>
@@ -13467,10 +13451,10 @@
       <c r="R188">
         <v>76</v>
       </c>
-      <c r="S188" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T188" s="7" t="s">
+      <c r="S188" t="s">
+        <v>12</v>
+      </c>
+      <c r="T188" t="s">
         <v>124</v>
       </c>
     </row>
@@ -13523,10 +13507,10 @@
       <c r="R189">
         <v>76</v>
       </c>
-      <c r="S189" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T189" s="7" t="s">
+      <c r="S189" t="s">
+        <v>12</v>
+      </c>
+      <c r="T189" t="s">
         <v>155</v>
       </c>
     </row>
@@ -13579,10 +13563,10 @@
       <c r="R190">
         <v>76</v>
       </c>
-      <c r="S190" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T190" s="7" t="s">
+      <c r="S190" t="s">
+        <v>12</v>
+      </c>
+      <c r="T190" t="s">
         <v>49</v>
       </c>
     </row>
@@ -13635,10 +13619,10 @@
       <c r="R191">
         <v>76</v>
       </c>
-      <c r="S191" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T191" s="7" t="s">
+      <c r="S191" t="s">
+        <v>12</v>
+      </c>
+      <c r="T191" t="s">
         <v>92</v>
       </c>
     </row>
@@ -13691,10 +13675,10 @@
       <c r="R192">
         <v>76</v>
       </c>
-      <c r="S192" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T192" s="7" t="s">
+      <c r="S192" t="s">
+        <v>12</v>
+      </c>
+      <c r="T192" t="s">
         <v>101</v>
       </c>
     </row>
@@ -13747,10 +13731,10 @@
       <c r="R193">
         <v>76</v>
       </c>
-      <c r="S193" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T193" s="7" t="s">
+      <c r="S193" t="s">
+        <v>12</v>
+      </c>
+      <c r="T193" t="s">
         <v>122</v>
       </c>
     </row>
@@ -13803,10 +13787,10 @@
       <c r="R194">
         <v>76</v>
       </c>
-      <c r="S194" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T194" s="7" t="s">
+      <c r="S194" t="s">
+        <v>12</v>
+      </c>
+      <c r="T194" t="s">
         <v>31</v>
       </c>
     </row>
@@ -13859,10 +13843,10 @@
       <c r="R195">
         <v>76</v>
       </c>
-      <c r="S195" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T195" s="7" t="s">
+      <c r="S195" t="s">
+        <v>12</v>
+      </c>
+      <c r="T195" t="s">
         <v>30</v>
       </c>
     </row>
@@ -13915,10 +13899,10 @@
       <c r="R196">
         <v>76</v>
       </c>
-      <c r="S196" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T196" s="7" t="s">
+      <c r="S196" t="s">
+        <v>12</v>
+      </c>
+      <c r="T196" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13971,10 +13955,10 @@
       <c r="R197">
         <v>76</v>
       </c>
-      <c r="S197" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T197" s="7" t="s">
+      <c r="S197" t="s">
+        <v>12</v>
+      </c>
+      <c r="T197" t="s">
         <v>157</v>
       </c>
     </row>
@@ -14027,10 +14011,10 @@
       <c r="R198">
         <v>76</v>
       </c>
-      <c r="S198" s="7" t="s">
+      <c r="S198" t="s">
         <v>33</v>
       </c>
-      <c r="T198" s="7" t="s">
+      <c r="T198" t="s">
         <v>158</v>
       </c>
     </row>
@@ -14083,10 +14067,10 @@
       <c r="R199">
         <v>76</v>
       </c>
-      <c r="S199" s="7" t="s">
+      <c r="S199" t="s">
         <v>27</v>
       </c>
-      <c r="T199" s="7" t="s">
+      <c r="T199" t="s">
         <v>133</v>
       </c>
     </row>
@@ -14139,10 +14123,10 @@
       <c r="R200">
         <v>76</v>
       </c>
-      <c r="S200" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T200" s="7" t="s">
+      <c r="S200" t="s">
+        <v>12</v>
+      </c>
+      <c r="T200" t="s">
         <v>159</v>
       </c>
     </row>
@@ -14195,10 +14179,10 @@
       <c r="R201">
         <v>76</v>
       </c>
-      <c r="S201" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T201" s="7" t="s">
+      <c r="S201" t="s">
+        <v>12</v>
+      </c>
+      <c r="T201" t="s">
         <v>160</v>
       </c>
     </row>
@@ -14251,10 +14235,10 @@
       <c r="R202">
         <v>76</v>
       </c>
-      <c r="S202" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T202" s="7" t="s">
+      <c r="S202" t="s">
+        <v>12</v>
+      </c>
+      <c r="T202" t="s">
         <v>161</v>
       </c>
     </row>
@@ -14307,10 +14291,10 @@
       <c r="R203">
         <v>76</v>
       </c>
-      <c r="S203" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T203" s="7" t="s">
+      <c r="S203" t="s">
+        <v>12</v>
+      </c>
+      <c r="T203" t="s">
         <v>162</v>
       </c>
     </row>
@@ -14363,10 +14347,10 @@
       <c r="R204">
         <v>76</v>
       </c>
-      <c r="S204" s="7" t="s">
+      <c r="S204" t="s">
         <v>33</v>
       </c>
-      <c r="T204" s="7" t="s">
+      <c r="T204" t="s">
         <v>148</v>
       </c>
     </row>
@@ -14419,10 +14403,10 @@
       <c r="R205">
         <v>76</v>
       </c>
-      <c r="S205" s="7" t="s">
+      <c r="S205" t="s">
         <v>27</v>
       </c>
-      <c r="T205" s="7" t="s">
+      <c r="T205" t="s">
         <v>163</v>
       </c>
     </row>
@@ -14475,10 +14459,10 @@
       <c r="R206">
         <v>76</v>
       </c>
-      <c r="S206" s="7" t="s">
+      <c r="S206" t="s">
         <v>27</v>
       </c>
-      <c r="T206" s="7" t="s">
+      <c r="T206" t="s">
         <v>146</v>
       </c>
     </row>
@@ -14531,10 +14515,10 @@
       <c r="R207">
         <v>76</v>
       </c>
-      <c r="S207" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T207" s="7" t="s">
+      <c r="S207" t="s">
+        <v>12</v>
+      </c>
+      <c r="T207" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14587,10 +14571,10 @@
       <c r="R208">
         <v>76</v>
       </c>
-      <c r="S208" s="7" t="s">
+      <c r="S208" t="s">
         <v>33</v>
       </c>
-      <c r="T208" s="7" t="s">
+      <c r="T208" t="s">
         <v>164</v>
       </c>
     </row>
@@ -14643,10 +14627,10 @@
       <c r="R209">
         <v>76</v>
       </c>
-      <c r="S209" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T209" s="7" t="s">
+      <c r="S209" t="s">
+        <v>12</v>
+      </c>
+      <c r="T209" t="s">
         <v>165</v>
       </c>
     </row>
@@ -14699,10 +14683,10 @@
       <c r="R210">
         <v>76</v>
       </c>
-      <c r="S210" s="7" t="s">
+      <c r="S210" t="s">
         <v>33</v>
       </c>
-      <c r="T210" s="7" t="s">
+      <c r="T210" t="s">
         <v>35</v>
       </c>
     </row>
@@ -14755,10 +14739,10 @@
       <c r="R211">
         <v>76</v>
       </c>
-      <c r="S211" s="7" t="s">
+      <c r="S211" t="s">
         <v>27</v>
       </c>
-      <c r="T211" s="7" t="s">
+      <c r="T211" t="s">
         <v>120</v>
       </c>
     </row>
@@ -14811,10 +14795,10 @@
       <c r="R212">
         <v>76</v>
       </c>
-      <c r="S212" s="7" t="s">
+      <c r="S212" t="s">
         <v>33</v>
       </c>
-      <c r="T212" s="7" t="s">
+      <c r="T212" t="s">
         <v>166</v>
       </c>
     </row>
@@ -14867,10 +14851,10 @@
       <c r="R213">
         <v>76</v>
       </c>
-      <c r="S213" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T213" s="7" t="s">
+      <c r="S213" t="s">
+        <v>12</v>
+      </c>
+      <c r="T213" t="s">
         <v>167</v>
       </c>
     </row>
@@ -14923,10 +14907,10 @@
       <c r="R214">
         <v>76</v>
       </c>
-      <c r="S214" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T214" s="7" t="s">
+      <c r="S214" t="s">
+        <v>12</v>
+      </c>
+      <c r="T214" t="s">
         <v>168</v>
       </c>
     </row>
@@ -14979,10 +14963,10 @@
       <c r="R215">
         <v>76</v>
       </c>
-      <c r="S215" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T215" s="7" t="s">
+      <c r="S215" t="s">
+        <v>12</v>
+      </c>
+      <c r="T215" t="s">
         <v>169</v>
       </c>
     </row>
@@ -15035,10 +15019,10 @@
       <c r="R216">
         <v>76</v>
       </c>
-      <c r="S216" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T216" s="7" t="s">
+      <c r="S216" t="s">
+        <v>12</v>
+      </c>
+      <c r="T216" t="s">
         <v>170</v>
       </c>
     </row>
@@ -15091,10 +15075,10 @@
       <c r="R217">
         <v>77</v>
       </c>
-      <c r="S217" s="7" t="s">
+      <c r="S217" t="s">
         <v>27</v>
       </c>
-      <c r="T217" s="7" t="s">
+      <c r="T217" t="s">
         <v>171</v>
       </c>
     </row>
@@ -15147,10 +15131,10 @@
       <c r="R218">
         <v>77</v>
       </c>
-      <c r="S218" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T218" s="7" t="s">
+      <c r="S218" t="s">
+        <v>12</v>
+      </c>
+      <c r="T218" t="s">
         <v>172</v>
       </c>
     </row>
@@ -15203,10 +15187,10 @@
       <c r="R219">
         <v>77</v>
       </c>
-      <c r="S219" s="7" t="s">
+      <c r="S219" t="s">
         <v>33</v>
       </c>
-      <c r="T219" s="7" t="s">
+      <c r="T219" t="s">
         <v>173</v>
       </c>
     </row>
@@ -15259,10 +15243,10 @@
       <c r="R220">
         <v>77</v>
       </c>
-      <c r="S220" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T220" s="7" t="s">
+      <c r="S220" t="s">
+        <v>12</v>
+      </c>
+      <c r="T220" t="s">
         <v>174</v>
       </c>
     </row>
@@ -15315,10 +15299,10 @@
       <c r="R221">
         <v>77</v>
       </c>
-      <c r="S221" s="7" t="s">
+      <c r="S221" t="s">
         <v>27</v>
       </c>
-      <c r="T221" s="7" t="s">
+      <c r="T221" t="s">
         <v>175</v>
       </c>
     </row>
@@ -15371,10 +15355,10 @@
       <c r="R222">
         <v>77</v>
       </c>
-      <c r="S222" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T222" s="7" t="s">
+      <c r="S222" t="s">
+        <v>12</v>
+      </c>
+      <c r="T222" t="s">
         <v>95</v>
       </c>
     </row>
@@ -15427,10 +15411,10 @@
       <c r="R223">
         <v>77</v>
       </c>
-      <c r="S223" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T223" s="7" t="s">
+      <c r="S223" t="s">
+        <v>12</v>
+      </c>
+      <c r="T223" t="s">
         <v>176</v>
       </c>
     </row>
@@ -15483,10 +15467,10 @@
       <c r="R224">
         <v>77</v>
       </c>
-      <c r="S224" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T224" s="7" t="s">
+      <c r="S224" t="s">
+        <v>12</v>
+      </c>
+      <c r="T224" t="s">
         <v>177</v>
       </c>
     </row>
@@ -15539,10 +15523,10 @@
       <c r="R225">
         <v>77</v>
       </c>
-      <c r="S225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T225" s="7" t="s">
+      <c r="S225" t="s">
+        <v>12</v>
+      </c>
+      <c r="T225" t="s">
         <v>178</v>
       </c>
     </row>
@@ -15595,10 +15579,10 @@
       <c r="R226">
         <v>77</v>
       </c>
-      <c r="S226" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T226" s="7" t="s">
+      <c r="S226" t="s">
+        <v>12</v>
+      </c>
+      <c r="T226" t="s">
         <v>179</v>
       </c>
     </row>
@@ -15651,10 +15635,10 @@
       <c r="R227">
         <v>77</v>
       </c>
-      <c r="S227" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T227" s="7" t="s">
+      <c r="S227" t="s">
+        <v>12</v>
+      </c>
+      <c r="T227" t="s">
         <v>180</v>
       </c>
     </row>
@@ -15707,10 +15691,10 @@
       <c r="R228">
         <v>77</v>
       </c>
-      <c r="S228" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T228" s="7" t="s">
+      <c r="S228" t="s">
+        <v>12</v>
+      </c>
+      <c r="T228" t="s">
         <v>181</v>
       </c>
     </row>
@@ -15763,10 +15747,10 @@
       <c r="R229">
         <v>77</v>
       </c>
-      <c r="S229" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T229" s="7" t="s">
+      <c r="S229" t="s">
+        <v>12</v>
+      </c>
+      <c r="T229" t="s">
         <v>182</v>
       </c>
     </row>
@@ -15819,10 +15803,10 @@
       <c r="R230">
         <v>77</v>
       </c>
-      <c r="S230" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T230" s="7" t="s">
+      <c r="S230" t="s">
+        <v>12</v>
+      </c>
+      <c r="T230" t="s">
         <v>183</v>
       </c>
     </row>
@@ -15875,10 +15859,10 @@
       <c r="R231">
         <v>77</v>
       </c>
-      <c r="S231" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T231" s="7" t="s">
+      <c r="S231" t="s">
+        <v>12</v>
+      </c>
+      <c r="T231" t="s">
         <v>184</v>
       </c>
     </row>
@@ -15931,10 +15915,10 @@
       <c r="R232">
         <v>77</v>
       </c>
-      <c r="S232" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T232" s="7" t="s">
+      <c r="S232" t="s">
+        <v>12</v>
+      </c>
+      <c r="T232" t="s">
         <v>185</v>
       </c>
     </row>
@@ -15987,10 +15971,10 @@
       <c r="R233">
         <v>77</v>
       </c>
-      <c r="S233" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T233" s="7" t="s">
+      <c r="S233" t="s">
+        <v>12</v>
+      </c>
+      <c r="T233" t="s">
         <v>186</v>
       </c>
     </row>
@@ -16043,10 +16027,10 @@
       <c r="R234">
         <v>77</v>
       </c>
-      <c r="S234" s="7" t="s">
+      <c r="S234" t="s">
         <v>33</v>
       </c>
-      <c r="T234" s="7" t="s">
+      <c r="T234" t="s">
         <v>187</v>
       </c>
     </row>
@@ -16099,10 +16083,10 @@
       <c r="R235">
         <v>77</v>
       </c>
-      <c r="S235" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T235" s="7" t="s">
+      <c r="S235" t="s">
+        <v>12</v>
+      </c>
+      <c r="T235" t="s">
         <v>188</v>
       </c>
     </row>
@@ -16155,10 +16139,10 @@
       <c r="R236">
         <v>77</v>
       </c>
-      <c r="S236" s="7" t="s">
+      <c r="S236" t="s">
         <v>27</v>
       </c>
-      <c r="T236" s="7" t="s">
+      <c r="T236" t="s">
         <v>189</v>
       </c>
     </row>
@@ -16211,10 +16195,10 @@
       <c r="R237">
         <v>77</v>
       </c>
-      <c r="S237" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T237" s="7" t="s">
+      <c r="S237" t="s">
+        <v>12</v>
+      </c>
+      <c r="T237" t="s">
         <v>190</v>
       </c>
     </row>
@@ -16267,10 +16251,10 @@
       <c r="R238">
         <v>77</v>
       </c>
-      <c r="S238" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T238" s="7" t="s">
+      <c r="S238" t="s">
+        <v>12</v>
+      </c>
+      <c r="T238" t="s">
         <v>156</v>
       </c>
     </row>
@@ -16323,10 +16307,10 @@
       <c r="R239">
         <v>77</v>
       </c>
-      <c r="S239" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T239" s="7" t="s">
+      <c r="S239" t="s">
+        <v>12</v>
+      </c>
+      <c r="T239" t="s">
         <v>191</v>
       </c>
     </row>
@@ -16379,10 +16363,10 @@
       <c r="R240">
         <v>77</v>
       </c>
-      <c r="S240" s="7" t="s">
+      <c r="S240" t="s">
         <v>27</v>
       </c>
-      <c r="T240" s="7" t="s">
+      <c r="T240" t="s">
         <v>192</v>
       </c>
     </row>
@@ -16435,10 +16419,10 @@
       <c r="R241">
         <v>77</v>
       </c>
-      <c r="S241" s="7" t="s">
+      <c r="S241" t="s">
         <v>33</v>
       </c>
-      <c r="T241" s="7" t="s">
+      <c r="T241" t="s">
         <v>129</v>
       </c>
     </row>
@@ -16491,10 +16475,10 @@
       <c r="R242">
         <v>77</v>
       </c>
-      <c r="S242" s="7" t="s">
+      <c r="S242" t="s">
         <v>27</v>
       </c>
-      <c r="T242" s="7" t="s">
+      <c r="T242" t="s">
         <v>193</v>
       </c>
     </row>
@@ -16547,10 +16531,10 @@
       <c r="R243">
         <v>77</v>
       </c>
-      <c r="S243" s="7" t="s">
+      <c r="S243" t="s">
         <v>33</v>
       </c>
-      <c r="T243" s="7" t="s">
+      <c r="T243" t="s">
         <v>194</v>
       </c>
     </row>
@@ -16603,10 +16587,10 @@
       <c r="R244">
         <v>77</v>
       </c>
-      <c r="S244" s="7" t="s">
+      <c r="S244" t="s">
         <v>27</v>
       </c>
-      <c r="T244" s="7" t="s">
+      <c r="T244" t="s">
         <v>195</v>
       </c>
     </row>
@@ -16659,10 +16643,10 @@
       <c r="R245">
         <v>78</v>
       </c>
-      <c r="S245" s="7" t="s">
+      <c r="S245" t="s">
         <v>33</v>
       </c>
-      <c r="T245" s="7" t="s">
+      <c r="T245" t="s">
         <v>196</v>
       </c>
     </row>
@@ -16715,10 +16699,10 @@
       <c r="R246">
         <v>78</v>
       </c>
-      <c r="S246" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T246" s="7" t="s">
+      <c r="S246" t="s">
+        <v>12</v>
+      </c>
+      <c r="T246" t="s">
         <v>197</v>
       </c>
     </row>
@@ -16771,10 +16755,10 @@
       <c r="R247">
         <v>78</v>
       </c>
-      <c r="S247" s="7" t="s">
+      <c r="S247" t="s">
         <v>27</v>
       </c>
-      <c r="T247" s="7" t="s">
+      <c r="T247" t="s">
         <v>198</v>
       </c>
     </row>
@@ -16827,10 +16811,10 @@
       <c r="R248">
         <v>78</v>
       </c>
-      <c r="S248" s="7" t="s">
+      <c r="S248" t="s">
         <v>27</v>
       </c>
-      <c r="T248" s="7" t="s">
+      <c r="T248" t="s">
         <v>199</v>
       </c>
     </row>
@@ -16883,10 +16867,10 @@
       <c r="R249">
         <v>78</v>
       </c>
-      <c r="S249" s="7" t="s">
+      <c r="S249" t="s">
         <v>27</v>
       </c>
-      <c r="T249" s="7" t="s">
+      <c r="T249" t="s">
         <v>151</v>
       </c>
     </row>
@@ -16939,10 +16923,10 @@
       <c r="R250">
         <v>78</v>
       </c>
-      <c r="S250" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T250" s="7" t="s">
+      <c r="S250" t="s">
+        <v>12</v>
+      </c>
+      <c r="T250" t="s">
         <v>200</v>
       </c>
     </row>
@@ -16995,10 +16979,10 @@
       <c r="R251">
         <v>78</v>
       </c>
-      <c r="S251" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T251" s="7" t="s">
+      <c r="S251" t="s">
+        <v>12</v>
+      </c>
+      <c r="T251" t="s">
         <v>201</v>
       </c>
     </row>
@@ -17051,10 +17035,10 @@
       <c r="R252">
         <v>78</v>
       </c>
-      <c r="S252" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T252" s="7" t="s">
+      <c r="S252" t="s">
+        <v>12</v>
+      </c>
+      <c r="T252" t="s">
         <v>202</v>
       </c>
     </row>
@@ -17107,10 +17091,10 @@
       <c r="R253">
         <v>78</v>
       </c>
-      <c r="S253" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T253" s="7" t="s">
+      <c r="S253" t="s">
+        <v>12</v>
+      </c>
+      <c r="T253" t="s">
         <v>203</v>
       </c>
     </row>
@@ -17163,10 +17147,10 @@
       <c r="R254">
         <v>78</v>
       </c>
-      <c r="S254" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T254" s="7" t="s">
+      <c r="S254" t="s">
+        <v>12</v>
+      </c>
+      <c r="T254" t="s">
         <v>91</v>
       </c>
     </row>
@@ -17219,10 +17203,10 @@
       <c r="R255">
         <v>78</v>
       </c>
-      <c r="S255" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T255" s="7" t="s">
+      <c r="S255" t="s">
+        <v>12</v>
+      </c>
+      <c r="T255" t="s">
         <v>204</v>
       </c>
     </row>
@@ -17275,10 +17259,10 @@
       <c r="R256">
         <v>78</v>
       </c>
-      <c r="S256" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T256" s="7" t="s">
+      <c r="S256" t="s">
+        <v>12</v>
+      </c>
+      <c r="T256" t="s">
         <v>205</v>
       </c>
     </row>
@@ -17331,10 +17315,10 @@
       <c r="R257">
         <v>78</v>
       </c>
-      <c r="S257" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T257" s="7" t="s">
+      <c r="S257" t="s">
+        <v>12</v>
+      </c>
+      <c r="T257" t="s">
         <v>206</v>
       </c>
     </row>
@@ -17387,10 +17371,10 @@
       <c r="R258">
         <v>78</v>
       </c>
-      <c r="S258" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T258" s="7" t="s">
+      <c r="S258" t="s">
+        <v>12</v>
+      </c>
+      <c r="T258" t="s">
         <v>207</v>
       </c>
     </row>
@@ -17443,10 +17427,10 @@
       <c r="R259">
         <v>78</v>
       </c>
-      <c r="S259" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T259" s="7" t="s">
+      <c r="S259" t="s">
+        <v>12</v>
+      </c>
+      <c r="T259" t="s">
         <v>208</v>
       </c>
     </row>
@@ -17499,10 +17483,10 @@
       <c r="R260">
         <v>78</v>
       </c>
-      <c r="S260" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T260" s="7" t="s">
+      <c r="S260" t="s">
+        <v>12</v>
+      </c>
+      <c r="T260" t="s">
         <v>209</v>
       </c>
     </row>
@@ -17555,10 +17539,10 @@
       <c r="R261">
         <v>78</v>
       </c>
-      <c r="S261" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T261" s="7" t="s">
+      <c r="S261" t="s">
+        <v>12</v>
+      </c>
+      <c r="T261" t="s">
         <v>210</v>
       </c>
     </row>
@@ -17611,10 +17595,10 @@
       <c r="R262">
         <v>78</v>
       </c>
-      <c r="S262" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T262" s="7" t="s">
+      <c r="S262" t="s">
+        <v>12</v>
+      </c>
+      <c r="T262" t="s">
         <v>211</v>
       </c>
     </row>
@@ -17667,10 +17651,10 @@
       <c r="R263">
         <v>78</v>
       </c>
-      <c r="S263" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T263" s="7" t="s">
+      <c r="S263" t="s">
+        <v>12</v>
+      </c>
+      <c r="T263" t="s">
         <v>184</v>
       </c>
     </row>
@@ -17723,10 +17707,10 @@
       <c r="R264">
         <v>78</v>
       </c>
-      <c r="S264" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T264" s="7" t="s">
+      <c r="S264" t="s">
+        <v>12</v>
+      </c>
+      <c r="T264" t="s">
         <v>212</v>
       </c>
     </row>
@@ -17779,10 +17763,10 @@
       <c r="R265">
         <v>78</v>
       </c>
-      <c r="S265" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T265" s="7" t="s">
+      <c r="S265" t="s">
+        <v>12</v>
+      </c>
+      <c r="T265" t="s">
         <v>213</v>
       </c>
     </row>
@@ -17835,10 +17819,10 @@
       <c r="R266">
         <v>78</v>
       </c>
-      <c r="S266" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T266" s="7" t="s">
+      <c r="S266" t="s">
+        <v>12</v>
+      </c>
+      <c r="T266" t="s">
         <v>214</v>
       </c>
     </row>
@@ -17891,10 +17875,10 @@
       <c r="R267">
         <v>78</v>
       </c>
-      <c r="S267" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T267" s="7" t="s">
+      <c r="S267" t="s">
+        <v>12</v>
+      </c>
+      <c r="T267" t="s">
         <v>156</v>
       </c>
     </row>
@@ -17947,10 +17931,10 @@
       <c r="R268">
         <v>78</v>
       </c>
-      <c r="S268" s="7" t="s">
+      <c r="S268" t="s">
         <v>27</v>
       </c>
-      <c r="T268" s="7" t="s">
+      <c r="T268" t="s">
         <v>45</v>
       </c>
     </row>
@@ -18003,10 +17987,10 @@
       <c r="R269">
         <v>78</v>
       </c>
-      <c r="S269" s="7" t="s">
+      <c r="S269" t="s">
         <v>27</v>
       </c>
-      <c r="T269" s="7" t="s">
+      <c r="T269" t="s">
         <v>215</v>
       </c>
     </row>
@@ -18059,10 +18043,10 @@
       <c r="R270">
         <v>78</v>
       </c>
-      <c r="S270" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T270" s="7" t="s">
+      <c r="S270" t="s">
+        <v>12</v>
+      </c>
+      <c r="T270" t="s">
         <v>216</v>
       </c>
     </row>
@@ -18115,10 +18099,10 @@
       <c r="R271">
         <v>78</v>
       </c>
-      <c r="S271" s="7" t="s">
+      <c r="S271" t="s">
         <v>27</v>
       </c>
-      <c r="T271" s="7" t="s">
+      <c r="T271" t="s">
         <v>217</v>
       </c>
     </row>
@@ -18171,10 +18155,10 @@
       <c r="R272">
         <v>78</v>
       </c>
-      <c r="S272" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T272" s="7" t="s">
+      <c r="S272" t="s">
+        <v>12</v>
+      </c>
+      <c r="T272" t="s">
         <v>218</v>
       </c>
     </row>
@@ -18227,10 +18211,10 @@
       <c r="R273">
         <v>78</v>
       </c>
-      <c r="S273" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T273" s="7" t="s">
+      <c r="S273" t="s">
+        <v>12</v>
+      </c>
+      <c r="T273" t="s">
         <v>219</v>
       </c>
     </row>
@@ -18283,10 +18267,10 @@
       <c r="R274">
         <v>78</v>
       </c>
-      <c r="S274" s="7" t="s">
+      <c r="S274" t="s">
         <v>27</v>
       </c>
-      <c r="T274" s="7" t="s">
+      <c r="T274" t="s">
         <v>220</v>
       </c>
     </row>
@@ -18339,10 +18323,10 @@
       <c r="R275">
         <v>78</v>
       </c>
-      <c r="S275" s="7" t="s">
+      <c r="S275" t="s">
         <v>33</v>
       </c>
-      <c r="T275" s="7" t="s">
+      <c r="T275" t="s">
         <v>221</v>
       </c>
     </row>
@@ -18395,10 +18379,10 @@
       <c r="R276">
         <v>78</v>
       </c>
-      <c r="S276" s="7" t="s">
+      <c r="S276" t="s">
         <v>33</v>
       </c>
-      <c r="T276" s="7" t="s">
+      <c r="T276" t="s">
         <v>222</v>
       </c>
     </row>
@@ -18451,10 +18435,10 @@
       <c r="R277">
         <v>78</v>
       </c>
-      <c r="S277" s="7" t="s">
+      <c r="S277" t="s">
         <v>33</v>
       </c>
-      <c r="T277" s="7" t="s">
+      <c r="T277" t="s">
         <v>223</v>
       </c>
     </row>
@@ -18507,10 +18491,10 @@
       <c r="R278">
         <v>78</v>
       </c>
-      <c r="S278" s="7" t="s">
+      <c r="S278" t="s">
         <v>33</v>
       </c>
-      <c r="T278" s="7" t="s">
+      <c r="T278" t="s">
         <v>224</v>
       </c>
     </row>
@@ -18563,10 +18547,10 @@
       <c r="R279">
         <v>78</v>
       </c>
-      <c r="S279" s="7" t="s">
+      <c r="S279" t="s">
         <v>33</v>
       </c>
-      <c r="T279" s="7" t="s">
+      <c r="T279" t="s">
         <v>225</v>
       </c>
     </row>
@@ -18619,10 +18603,10 @@
       <c r="R280">
         <v>78</v>
       </c>
-      <c r="S280" s="7" t="s">
+      <c r="S280" t="s">
         <v>27</v>
       </c>
-      <c r="T280" s="7" t="s">
+      <c r="T280" t="s">
         <v>226</v>
       </c>
     </row>
@@ -18675,10 +18659,10 @@
       <c r="R281">
         <v>79</v>
       </c>
-      <c r="S281" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T281" s="7" t="s">
+      <c r="S281" t="s">
+        <v>12</v>
+      </c>
+      <c r="T281" t="s">
         <v>227</v>
       </c>
     </row>
@@ -18731,10 +18715,10 @@
       <c r="R282">
         <v>79</v>
       </c>
-      <c r="S282" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T282" s="7" t="s">
+      <c r="S282" t="s">
+        <v>12</v>
+      </c>
+      <c r="T282" t="s">
         <v>228</v>
       </c>
     </row>
@@ -18787,10 +18771,10 @@
       <c r="R283">
         <v>79</v>
       </c>
-      <c r="S283" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T283" s="7" t="s">
+      <c r="S283" t="s">
+        <v>12</v>
+      </c>
+      <c r="T283" t="s">
         <v>229</v>
       </c>
     </row>
@@ -18843,10 +18827,10 @@
       <c r="R284">
         <v>79</v>
       </c>
-      <c r="S284" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T284" s="7" t="s">
+      <c r="S284" t="s">
+        <v>12</v>
+      </c>
+      <c r="T284" t="s">
         <v>230</v>
       </c>
     </row>
@@ -18899,10 +18883,10 @@
       <c r="R285">
         <v>79</v>
       </c>
-      <c r="S285" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T285" s="7" t="s">
+      <c r="S285" t="s">
+        <v>12</v>
+      </c>
+      <c r="T285" t="s">
         <v>231</v>
       </c>
     </row>
@@ -18955,10 +18939,10 @@
       <c r="R286">
         <v>79</v>
       </c>
-      <c r="S286" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T286" s="7" t="s">
+      <c r="S286" t="s">
+        <v>12</v>
+      </c>
+      <c r="T286" t="s">
         <v>95</v>
       </c>
     </row>
@@ -19011,10 +18995,10 @@
       <c r="R287">
         <v>79</v>
       </c>
-      <c r="S287" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T287" s="7" t="s">
+      <c r="S287" t="s">
+        <v>12</v>
+      </c>
+      <c r="T287" t="s">
         <v>232</v>
       </c>
     </row>
@@ -19067,10 +19051,10 @@
       <c r="R288">
         <v>79</v>
       </c>
-      <c r="S288" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T288" s="7" t="s">
+      <c r="S288" t="s">
+        <v>12</v>
+      </c>
+      <c r="T288" t="s">
         <v>233</v>
       </c>
     </row>
@@ -19123,10 +19107,10 @@
       <c r="R289">
         <v>79</v>
       </c>
-      <c r="S289" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T289" s="7" t="s">
+      <c r="S289" t="s">
+        <v>12</v>
+      </c>
+      <c r="T289" t="s">
         <v>234</v>
       </c>
     </row>
@@ -19179,10 +19163,10 @@
       <c r="R290">
         <v>79</v>
       </c>
-      <c r="S290" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T290" s="7" t="s">
+      <c r="S290" t="s">
+        <v>12</v>
+      </c>
+      <c r="T290" t="s">
         <v>26</v>
       </c>
     </row>
@@ -19235,10 +19219,10 @@
       <c r="R291">
         <v>79</v>
       </c>
-      <c r="S291" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T291" s="7" t="s">
+      <c r="S291" t="s">
+        <v>12</v>
+      </c>
+      <c r="T291" t="s">
         <v>52</v>
       </c>
     </row>
@@ -19291,10 +19275,10 @@
       <c r="R292">
         <v>79</v>
       </c>
-      <c r="S292" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T292" s="7" t="s">
+      <c r="S292" t="s">
+        <v>12</v>
+      </c>
+      <c r="T292" t="s">
         <v>235</v>
       </c>
     </row>
@@ -19347,10 +19331,10 @@
       <c r="R293">
         <v>79</v>
       </c>
-      <c r="S293" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T293" s="7" t="s">
+      <c r="S293" t="s">
+        <v>12</v>
+      </c>
+      <c r="T293" t="s">
         <v>236</v>
       </c>
     </row>
@@ -19403,10 +19387,10 @@
       <c r="R294">
         <v>79</v>
       </c>
-      <c r="S294" s="7" t="s">
+      <c r="S294" t="s">
         <v>33</v>
       </c>
-      <c r="T294" s="7" t="s">
+      <c r="T294" t="s">
         <v>237</v>
       </c>
     </row>
@@ -19459,10 +19443,10 @@
       <c r="R295">
         <v>79</v>
       </c>
-      <c r="S295" s="7" t="s">
+      <c r="S295" t="s">
         <v>27</v>
       </c>
-      <c r="T295" s="7" t="s">
+      <c r="T295" t="s">
         <v>238</v>
       </c>
     </row>
@@ -19515,10 +19499,10 @@
       <c r="R296">
         <v>79</v>
       </c>
-      <c r="S296" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T296" s="7" t="s">
+      <c r="S296" t="s">
+        <v>12</v>
+      </c>
+      <c r="T296" t="s">
         <v>239</v>
       </c>
     </row>
@@ -19571,10 +19555,10 @@
       <c r="R297">
         <v>79</v>
       </c>
-      <c r="S297" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T297" s="7" t="s">
+      <c r="S297" t="s">
+        <v>12</v>
+      </c>
+      <c r="T297" t="s">
         <v>240</v>
       </c>
     </row>
@@ -19627,10 +19611,10 @@
       <c r="R298">
         <v>79</v>
       </c>
-      <c r="S298" s="7" t="s">
+      <c r="S298" t="s">
         <v>33</v>
       </c>
-      <c r="T298" s="7" t="s">
+      <c r="T298" t="s">
         <v>241</v>
       </c>
     </row>
@@ -19683,10 +19667,10 @@
       <c r="R299">
         <v>79</v>
       </c>
-      <c r="S299" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T299" s="7" t="s">
+      <c r="S299" t="s">
+        <v>12</v>
+      </c>
+      <c r="T299" t="s">
         <v>242</v>
       </c>
     </row>
@@ -19739,10 +19723,10 @@
       <c r="R300">
         <v>79</v>
       </c>
-      <c r="S300" s="7" t="s">
+      <c r="S300" t="s">
         <v>33</v>
       </c>
-      <c r="T300" s="7" t="s">
+      <c r="T300" t="s">
         <v>35</v>
       </c>
     </row>
@@ -19795,10 +19779,10 @@
       <c r="R301">
         <v>79</v>
       </c>
-      <c r="S301" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T301" s="7" t="s">
+      <c r="S301" t="s">
+        <v>12</v>
+      </c>
+      <c r="T301" t="s">
         <v>200</v>
       </c>
     </row>
@@ -19851,10 +19835,10 @@
       <c r="R302">
         <v>79</v>
       </c>
-      <c r="S302" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T302" s="7" t="s">
+      <c r="S302" t="s">
+        <v>12</v>
+      </c>
+      <c r="T302" t="s">
         <v>243</v>
       </c>
     </row>
@@ -19907,10 +19891,10 @@
       <c r="R303">
         <v>79</v>
       </c>
-      <c r="S303" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T303" s="7" t="s">
+      <c r="S303" t="s">
+        <v>12</v>
+      </c>
+      <c r="T303" t="s">
         <v>244</v>
       </c>
     </row>
@@ -19963,10 +19947,10 @@
       <c r="R304">
         <v>79</v>
       </c>
-      <c r="S304" s="7" t="s">
+      <c r="S304" t="s">
         <v>27</v>
       </c>
-      <c r="T304" s="7" t="s">
+      <c r="T304" t="s">
         <v>245</v>
       </c>
     </row>
@@ -20019,10 +20003,10 @@
       <c r="R305">
         <v>79</v>
       </c>
-      <c r="S305" s="7" t="s">
+      <c r="S305" t="s">
         <v>33</v>
       </c>
-      <c r="T305" s="7" t="s">
+      <c r="T305" t="s">
         <v>246</v>
       </c>
     </row>
@@ -20075,10 +20059,10 @@
       <c r="R306">
         <v>79</v>
       </c>
-      <c r="S306" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T306" s="7" t="s">
+      <c r="S306" t="s">
+        <v>12</v>
+      </c>
+      <c r="T306" t="s">
         <v>247</v>
       </c>
     </row>
@@ -20131,10 +20115,10 @@
       <c r="R307">
         <v>79</v>
       </c>
-      <c r="S307" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T307" s="7" t="s">
+      <c r="S307" t="s">
+        <v>12</v>
+      </c>
+      <c r="T307" t="s">
         <v>248</v>
       </c>
     </row>
@@ -20187,10 +20171,10 @@
       <c r="R308">
         <v>79</v>
       </c>
-      <c r="S308" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T308" s="7" t="s">
+      <c r="S308" t="s">
+        <v>12</v>
+      </c>
+      <c r="T308" t="s">
         <v>249</v>
       </c>
     </row>
@@ -20243,10 +20227,10 @@
       <c r="R309">
         <v>79</v>
       </c>
-      <c r="S309" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T309" s="7" t="s">
+      <c r="S309" t="s">
+        <v>12</v>
+      </c>
+      <c r="T309" t="s">
         <v>250</v>
       </c>
     </row>
@@ -20299,10 +20283,10 @@
       <c r="R310">
         <v>80</v>
       </c>
-      <c r="S310" s="7" t="s">
+      <c r="S310" t="s">
         <v>33</v>
       </c>
-      <c r="T310" s="7" t="s">
+      <c r="T310" t="s">
         <v>158</v>
       </c>
     </row>
@@ -20355,10 +20339,10 @@
       <c r="R311">
         <v>80</v>
       </c>
-      <c r="S311" s="7" t="s">
+      <c r="S311" t="s">
         <v>27</v>
       </c>
-      <c r="T311" s="7" t="s">
+      <c r="T311" t="s">
         <v>251</v>
       </c>
     </row>
@@ -20411,10 +20395,10 @@
       <c r="R312">
         <v>80</v>
       </c>
-      <c r="S312" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T312" s="7" t="s">
+      <c r="S312" t="s">
+        <v>12</v>
+      </c>
+      <c r="T312" t="s">
         <v>156</v>
       </c>
     </row>
@@ -20467,10 +20451,10 @@
       <c r="R313">
         <v>80</v>
       </c>
-      <c r="S313" s="7" t="s">
+      <c r="S313" t="s">
         <v>27</v>
       </c>
-      <c r="T313" s="7" t="s">
+      <c r="T313" t="s">
         <v>252</v>
       </c>
     </row>
@@ -20523,10 +20507,10 @@
       <c r="R314">
         <v>80</v>
       </c>
-      <c r="S314" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T314" s="7" t="s">
+      <c r="S314" t="s">
+        <v>12</v>
+      </c>
+      <c r="T314" t="s">
         <v>248</v>
       </c>
     </row>
@@ -20579,10 +20563,10 @@
       <c r="R315">
         <v>80</v>
       </c>
-      <c r="S315" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T315" s="7" t="s">
+      <c r="S315" t="s">
+        <v>12</v>
+      </c>
+      <c r="T315" t="s">
         <v>253</v>
       </c>
     </row>
@@ -20635,10 +20619,10 @@
       <c r="R316">
         <v>80</v>
       </c>
-      <c r="S316" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T316" s="7" t="s">
+      <c r="S316" t="s">
+        <v>12</v>
+      </c>
+      <c r="T316" t="s">
         <v>207</v>
       </c>
     </row>
@@ -20691,10 +20675,10 @@
       <c r="R317">
         <v>80</v>
       </c>
-      <c r="S317" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T317" s="7" t="s">
+      <c r="S317" t="s">
+        <v>12</v>
+      </c>
+      <c r="T317" t="s">
         <v>210</v>
       </c>
     </row>
@@ -20747,10 +20731,10 @@
       <c r="R318">
         <v>80</v>
       </c>
-      <c r="S318" s="7" t="s">
+      <c r="S318" t="s">
         <v>33</v>
       </c>
-      <c r="T318" s="7" t="s">
+      <c r="T318" t="s">
         <v>254</v>
       </c>
     </row>
@@ -20803,10 +20787,10 @@
       <c r="R319">
         <v>80</v>
       </c>
-      <c r="S319" s="7" t="s">
+      <c r="S319" t="s">
         <v>27</v>
       </c>
-      <c r="T319" s="7" t="s">
+      <c r="T319" t="s">
         <v>255</v>
       </c>
     </row>
@@ -20859,10 +20843,10 @@
       <c r="R320">
         <v>80</v>
       </c>
-      <c r="S320" s="7" t="s">
+      <c r="S320" t="s">
         <v>27</v>
       </c>
-      <c r="T320" s="7" t="s">
+      <c r="T320" t="s">
         <v>256</v>
       </c>
     </row>
@@ -20915,10 +20899,10 @@
       <c r="R321">
         <v>80</v>
       </c>
-      <c r="S321" s="7" t="s">
+      <c r="S321" t="s">
         <v>27</v>
       </c>
-      <c r="T321" s="7" t="s">
+      <c r="T321" t="s">
         <v>257</v>
       </c>
     </row>
@@ -20971,10 +20955,10 @@
       <c r="R322">
         <v>80</v>
       </c>
-      <c r="S322" s="7" t="s">
+      <c r="S322" t="s">
         <v>27</v>
       </c>
-      <c r="T322" s="7" t="s">
+      <c r="T322" t="s">
         <v>146</v>
       </c>
     </row>
@@ -21027,10 +21011,10 @@
       <c r="R323">
         <v>80</v>
       </c>
-      <c r="S323" s="7" t="s">
+      <c r="S323" t="s">
         <v>27</v>
       </c>
-      <c r="T323" s="7" t="s">
+      <c r="T323" t="s">
         <v>258</v>
       </c>
     </row>
@@ -21083,10 +21067,10 @@
       <c r="R324">
         <v>80</v>
       </c>
-      <c r="S324" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T324" s="7" t="s">
+      <c r="S324" t="s">
+        <v>12</v>
+      </c>
+      <c r="T324" t="s">
         <v>131</v>
       </c>
     </row>
@@ -21139,10 +21123,10 @@
       <c r="R325">
         <v>80</v>
       </c>
-      <c r="S325" s="7" t="s">
+      <c r="S325" t="s">
         <v>27</v>
       </c>
-      <c r="T325" s="7" t="s">
+      <c r="T325" t="s">
         <v>245</v>
       </c>
     </row>
@@ -21195,10 +21179,10 @@
       <c r="R326">
         <v>80</v>
       </c>
-      <c r="S326" s="7" t="s">
+      <c r="S326" t="s">
         <v>33</v>
       </c>
-      <c r="T326" s="7" t="s">
+      <c r="T326" t="s">
         <v>259</v>
       </c>
     </row>
@@ -21251,10 +21235,10 @@
       <c r="R327">
         <v>80</v>
       </c>
-      <c r="S327" s="7" t="s">
+      <c r="S327" t="s">
         <v>33</v>
       </c>
-      <c r="T327" s="7" t="s">
+      <c r="T327" t="s">
         <v>260</v>
       </c>
     </row>
@@ -21307,10 +21291,10 @@
       <c r="R328">
         <v>80</v>
       </c>
-      <c r="S328" s="7" t="s">
+      <c r="S328" t="s">
         <v>33</v>
       </c>
-      <c r="T328" s="7" t="s">
+      <c r="T328" t="s">
         <v>261</v>
       </c>
     </row>
@@ -21363,10 +21347,10 @@
       <c r="R329">
         <v>80</v>
       </c>
-      <c r="S329" s="7" t="s">
+      <c r="S329" t="s">
         <v>33</v>
       </c>
-      <c r="T329" s="7" t="s">
+      <c r="T329" t="s">
         <v>262</v>
       </c>
     </row>
@@ -21419,10 +21403,10 @@
       <c r="R330">
         <v>80</v>
       </c>
-      <c r="S330" s="7" t="s">
+      <c r="S330" t="s">
         <v>27</v>
       </c>
-      <c r="T330" s="7" t="s">
+      <c r="T330" t="s">
         <v>263</v>
       </c>
     </row>
@@ -21475,10 +21459,10 @@
       <c r="R331">
         <v>80</v>
       </c>
-      <c r="S331" s="7" t="s">
+      <c r="S331" t="s">
         <v>27</v>
       </c>
-      <c r="T331" s="7" t="s">
+      <c r="T331" t="s">
         <v>192</v>
       </c>
     </row>
@@ -21531,10 +21515,10 @@
       <c r="R332">
         <v>80</v>
       </c>
-      <c r="S332" s="7" t="s">
+      <c r="S332" t="s">
         <v>33</v>
       </c>
-      <c r="T332" s="7" t="s">
+      <c r="T332" t="s">
         <v>265</v>
       </c>
     </row>
@@ -21587,10 +21571,10 @@
       <c r="R333">
         <v>80</v>
       </c>
-      <c r="S333" s="7" t="s">
+      <c r="S333" t="s">
         <v>27</v>
       </c>
-      <c r="T333" s="7" t="s">
+      <c r="T333" t="s">
         <v>266</v>
       </c>
     </row>
@@ -21643,10 +21627,10 @@
       <c r="R334">
         <v>80</v>
       </c>
-      <c r="S334" s="7" t="s">
+      <c r="S334" t="s">
         <v>27</v>
       </c>
-      <c r="T334" s="7" t="s">
+      <c r="T334" t="s">
         <v>267</v>
       </c>
     </row>
@@ -21699,10 +21683,10 @@
       <c r="R335">
         <v>80</v>
       </c>
-      <c r="S335" s="7" t="s">
+      <c r="S335" t="s">
         <v>33</v>
       </c>
-      <c r="T335" s="7" t="s">
+      <c r="T335" t="s">
         <v>268</v>
       </c>
     </row>
@@ -21755,10 +21739,10 @@
       <c r="R336">
         <v>80</v>
       </c>
-      <c r="S336" s="7" t="s">
+      <c r="S336" t="s">
         <v>27</v>
       </c>
-      <c r="T336" s="7" t="s">
+      <c r="T336" t="s">
         <v>270</v>
       </c>
     </row>
@@ -21811,10 +21795,10 @@
       <c r="R337">
         <v>81</v>
       </c>
-      <c r="S337" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T337" s="7" t="s">
+      <c r="S337" t="s">
+        <v>12</v>
+      </c>
+      <c r="T337" t="s">
         <v>271</v>
       </c>
     </row>
@@ -21867,10 +21851,10 @@
       <c r="R338">
         <v>81</v>
       </c>
-      <c r="S338" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T338" s="7" t="s">
+      <c r="S338" t="s">
+        <v>12</v>
+      </c>
+      <c r="T338" t="s">
         <v>180</v>
       </c>
     </row>
@@ -21923,10 +21907,10 @@
       <c r="R339">
         <v>81</v>
       </c>
-      <c r="S339" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T339" s="7" t="s">
+      <c r="S339" t="s">
+        <v>12</v>
+      </c>
+      <c r="T339" t="s">
         <v>272</v>
       </c>
     </row>
@@ -21979,10 +21963,10 @@
       <c r="R340">
         <v>81</v>
       </c>
-      <c r="S340" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T340" s="7" t="s">
+      <c r="S340" t="s">
+        <v>12</v>
+      </c>
+      <c r="T340" t="s">
         <v>248</v>
       </c>
     </row>
@@ -22035,10 +22019,10 @@
       <c r="R341">
         <v>81</v>
       </c>
-      <c r="S341" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T341" s="7" t="s">
+      <c r="S341" t="s">
+        <v>12</v>
+      </c>
+      <c r="T341" t="s">
         <v>271</v>
       </c>
     </row>
@@ -22091,10 +22075,10 @@
       <c r="R342">
         <v>81</v>
       </c>
-      <c r="S342" s="7" t="s">
+      <c r="S342" t="s">
         <v>27</v>
       </c>
-      <c r="T342" s="7" t="s">
+      <c r="T342" t="s">
         <v>273</v>
       </c>
     </row>
@@ -22147,10 +22131,10 @@
       <c r="R343">
         <v>81</v>
       </c>
-      <c r="S343" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T343" s="7" t="s">
+      <c r="S343" t="s">
+        <v>12</v>
+      </c>
+      <c r="T343" t="s">
         <v>274</v>
       </c>
     </row>
@@ -22203,10 +22187,10 @@
       <c r="R344">
         <v>81</v>
       </c>
-      <c r="S344" s="7" t="s">
+      <c r="S344" t="s">
         <v>27</v>
       </c>
-      <c r="T344" s="7" t="s">
+      <c r="T344" t="s">
         <v>275</v>
       </c>
     </row>
@@ -22259,10 +22243,10 @@
       <c r="R345">
         <v>81</v>
       </c>
-      <c r="S345" s="7" t="s">
+      <c r="S345" t="s">
         <v>27</v>
       </c>
-      <c r="T345" s="7" t="s">
+      <c r="T345" t="s">
         <v>134</v>
       </c>
     </row>
@@ -22315,10 +22299,10 @@
       <c r="R346">
         <v>81</v>
       </c>
-      <c r="S346" s="7" t="s">
+      <c r="S346" t="s">
         <v>27</v>
       </c>
-      <c r="T346" s="7" t="s">
+      <c r="T346" t="s">
         <v>276</v>
       </c>
     </row>
@@ -22371,10 +22355,10 @@
       <c r="R347">
         <v>81</v>
       </c>
-      <c r="S347" s="7" t="s">
+      <c r="S347" t="s">
         <v>27</v>
       </c>
-      <c r="T347" s="7" t="s">
+      <c r="T347" t="s">
         <v>277</v>
       </c>
     </row>
@@ -22427,10 +22411,10 @@
       <c r="R348">
         <v>81</v>
       </c>
-      <c r="S348" s="7" t="s">
+      <c r="S348" t="s">
         <v>27</v>
       </c>
-      <c r="T348" s="7" t="s">
+      <c r="T348" t="s">
         <v>278</v>
       </c>
     </row>
@@ -22483,10 +22467,10 @@
       <c r="R349">
         <v>81</v>
       </c>
-      <c r="S349" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T349" s="7" t="s">
+      <c r="S349" t="s">
+        <v>12</v>
+      </c>
+      <c r="T349" t="s">
         <v>279</v>
       </c>
     </row>
@@ -22539,10 +22523,10 @@
       <c r="R350">
         <v>81</v>
       </c>
-      <c r="S350" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T350" s="7" t="s">
+      <c r="S350" t="s">
+        <v>12</v>
+      </c>
+      <c r="T350" t="s">
         <v>280</v>
       </c>
     </row>
@@ -22595,10 +22579,10 @@
       <c r="R351">
         <v>81</v>
       </c>
-      <c r="S351" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T351" s="7" t="s">
+      <c r="S351" t="s">
+        <v>12</v>
+      </c>
+      <c r="T351" t="s">
         <v>281</v>
       </c>
     </row>
@@ -22651,10 +22635,10 @@
       <c r="R352">
         <v>81</v>
       </c>
-      <c r="S352" s="7" t="s">
+      <c r="S352" t="s">
         <v>33</v>
       </c>
-      <c r="T352" s="7" t="s">
+      <c r="T352" t="s">
         <v>282</v>
       </c>
     </row>
@@ -22707,10 +22691,10 @@
       <c r="R353">
         <v>81</v>
       </c>
-      <c r="S353" s="7" t="s">
+      <c r="S353" t="s">
         <v>27</v>
       </c>
-      <c r="T353" s="7" t="s">
+      <c r="T353" t="s">
         <v>284</v>
       </c>
     </row>
@@ -22763,10 +22747,10 @@
       <c r="R354">
         <v>81</v>
       </c>
-      <c r="S354" s="7" t="s">
+      <c r="S354" t="s">
         <v>27</v>
       </c>
-      <c r="T354" s="7" t="s">
+      <c r="T354" t="s">
         <v>146</v>
       </c>
     </row>
@@ -22819,10 +22803,10 @@
       <c r="R355">
         <v>81</v>
       </c>
-      <c r="S355" s="7" t="s">
+      <c r="S355" t="s">
         <v>27</v>
       </c>
-      <c r="T355" s="7" t="s">
+      <c r="T355" t="s">
         <v>285</v>
       </c>
     </row>
@@ -22875,10 +22859,10 @@
       <c r="R356">
         <v>81</v>
       </c>
-      <c r="S356" s="7" t="s">
+      <c r="S356" t="s">
         <v>27</v>
       </c>
-      <c r="T356" s="7" t="s">
+      <c r="T356" t="s">
         <v>256</v>
       </c>
     </row>
@@ -22929,10 +22913,10 @@
       <c r="R357">
         <v>81</v>
       </c>
-      <c r="S357" s="7" t="s">
+      <c r="S357" t="s">
         <v>33</v>
       </c>
-      <c r="T357" s="7" t="s">
+      <c r="T357" t="s">
         <v>286</v>
       </c>
     </row>
@@ -22985,10 +22969,10 @@
       <c r="R358">
         <v>81</v>
       </c>
-      <c r="S358" s="7" t="s">
+      <c r="S358" t="s">
         <v>33</v>
       </c>
-      <c r="T358" s="7" t="s">
+      <c r="T358" t="s">
         <v>287</v>
       </c>
     </row>
@@ -23041,10 +23025,10 @@
       <c r="R359">
         <v>81</v>
       </c>
-      <c r="S359" s="7" t="s">
+      <c r="S359" t="s">
         <v>27</v>
       </c>
-      <c r="T359" s="7" t="s">
+      <c r="T359" t="s">
         <v>288</v>
       </c>
     </row>
@@ -23097,10 +23081,10 @@
       <c r="R360">
         <v>81</v>
       </c>
-      <c r="S360" s="7" t="s">
+      <c r="S360" t="s">
         <v>27</v>
       </c>
-      <c r="T360" s="7" t="s">
+      <c r="T360" t="s">
         <v>289</v>
       </c>
     </row>
@@ -23153,10 +23137,10 @@
       <c r="R361">
         <v>81</v>
       </c>
-      <c r="S361" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T361" s="7" t="s">
+      <c r="S361" t="s">
+        <v>12</v>
+      </c>
+      <c r="T361" t="s">
         <v>140</v>
       </c>
     </row>
@@ -23209,10 +23193,10 @@
       <c r="R362">
         <v>81</v>
       </c>
-      <c r="S362" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T362" s="7" t="s">
+      <c r="S362" t="s">
+        <v>12</v>
+      </c>
+      <c r="T362" t="s">
         <v>290</v>
       </c>
     </row>
@@ -23265,10 +23249,10 @@
       <c r="R363">
         <v>81</v>
       </c>
-      <c r="S363" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T363" s="7" t="s">
+      <c r="S363" t="s">
+        <v>12</v>
+      </c>
+      <c r="T363" t="s">
         <v>291</v>
       </c>
     </row>
@@ -23321,10 +23305,10 @@
       <c r="R364">
         <v>81</v>
       </c>
-      <c r="S364" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T364" s="7" t="s">
+      <c r="S364" t="s">
+        <v>12</v>
+      </c>
+      <c r="T364" t="s">
         <v>292</v>
       </c>
     </row>
@@ -23377,10 +23361,10 @@
       <c r="R365">
         <v>82</v>
       </c>
-      <c r="S365" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T365" s="7" t="s">
+      <c r="S365" t="s">
+        <v>12</v>
+      </c>
+      <c r="T365" t="s">
         <v>293</v>
       </c>
     </row>
@@ -23433,10 +23417,10 @@
       <c r="R366">
         <v>82</v>
       </c>
-      <c r="S366" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T366" s="7" t="s">
+      <c r="S366" t="s">
+        <v>12</v>
+      </c>
+      <c r="T366" t="s">
         <v>294</v>
       </c>
     </row>
@@ -23489,10 +23473,10 @@
       <c r="R367">
         <v>82</v>
       </c>
-      <c r="S367" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T367" s="7" t="s">
+      <c r="S367" t="s">
+        <v>12</v>
+      </c>
+      <c r="T367" t="s">
         <v>295</v>
       </c>
     </row>
@@ -23545,10 +23529,10 @@
       <c r="R368">
         <v>82</v>
       </c>
-      <c r="S368" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T368" s="7" t="s">
+      <c r="S368" t="s">
+        <v>12</v>
+      </c>
+      <c r="T368" t="s">
         <v>296</v>
       </c>
     </row>
@@ -23601,10 +23585,10 @@
       <c r="R369">
         <v>82</v>
       </c>
-      <c r="S369" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T369" s="7" t="s">
+      <c r="S369" t="s">
+        <v>12</v>
+      </c>
+      <c r="T369" t="s">
         <v>297</v>
       </c>
     </row>
@@ -23657,10 +23641,10 @@
       <c r="R370">
         <v>82</v>
       </c>
-      <c r="S370" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T370" s="7" t="s">
+      <c r="S370" t="s">
+        <v>12</v>
+      </c>
+      <c r="T370" t="s">
         <v>250</v>
       </c>
     </row>
@@ -23713,10 +23697,10 @@
       <c r="R371">
         <v>82</v>
       </c>
-      <c r="S371" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T371" s="7" t="s">
+      <c r="S371" t="s">
+        <v>12</v>
+      </c>
+      <c r="T371" t="s">
         <v>298</v>
       </c>
     </row>
@@ -23769,10 +23753,10 @@
       <c r="R372">
         <v>82</v>
       </c>
-      <c r="S372" s="7" t="s">
+      <c r="S372" t="s">
         <v>33</v>
       </c>
-      <c r="T372" s="7" t="s">
+      <c r="T372" t="s">
         <v>300</v>
       </c>
     </row>
@@ -23825,10 +23809,10 @@
       <c r="R373">
         <v>82</v>
       </c>
-      <c r="S373" s="7" t="s">
+      <c r="S373" t="s">
         <v>27</v>
       </c>
-      <c r="T373" s="7" t="s">
+      <c r="T373" t="s">
         <v>301</v>
       </c>
     </row>
@@ -23881,10 +23865,10 @@
       <c r="R374">
         <v>82</v>
       </c>
-      <c r="S374" s="7" t="s">
+      <c r="S374" t="s">
         <v>27</v>
       </c>
-      <c r="T374" s="7" t="s">
+      <c r="T374" t="s">
         <v>302</v>
       </c>
     </row>
@@ -23937,10 +23921,10 @@
       <c r="R375">
         <v>82</v>
       </c>
-      <c r="S375" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T375" s="7" t="s">
+      <c r="S375" t="s">
+        <v>12</v>
+      </c>
+      <c r="T375" t="s">
         <v>303</v>
       </c>
     </row>
@@ -23993,10 +23977,10 @@
       <c r="R376">
         <v>82</v>
       </c>
-      <c r="S376" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T376" s="7" t="s">
+      <c r="S376" t="s">
+        <v>12</v>
+      </c>
+      <c r="T376" t="s">
         <v>304</v>
       </c>
     </row>
@@ -24047,10 +24031,10 @@
       <c r="R377">
         <v>82</v>
       </c>
-      <c r="S377" s="7" t="s">
+      <c r="S377" t="s">
         <v>27</v>
       </c>
-      <c r="T377" s="7" t="s">
+      <c r="T377" t="s">
         <v>305</v>
       </c>
     </row>
@@ -24103,10 +24087,10 @@
       <c r="R378">
         <v>82</v>
       </c>
-      <c r="S378" s="7" t="s">
+      <c r="S378" t="s">
         <v>27</v>
       </c>
-      <c r="T378" s="7" t="s">
+      <c r="T378" t="s">
         <v>270</v>
       </c>
     </row>
@@ -24159,10 +24143,10 @@
       <c r="R379">
         <v>82</v>
       </c>
-      <c r="S379" s="7" t="s">
+      <c r="S379" t="s">
         <v>27</v>
       </c>
-      <c r="T379" s="7" t="s">
+      <c r="T379" t="s">
         <v>146</v>
       </c>
     </row>
@@ -24215,10 +24199,10 @@
       <c r="R380">
         <v>82</v>
       </c>
-      <c r="S380" s="7" t="s">
+      <c r="S380" t="s">
         <v>27</v>
       </c>
-      <c r="T380" s="7" t="s">
+      <c r="T380" t="s">
         <v>133</v>
       </c>
     </row>
@@ -24271,10 +24255,10 @@
       <c r="R381">
         <v>82</v>
       </c>
-      <c r="S381" s="7" t="s">
+      <c r="S381" t="s">
         <v>27</v>
       </c>
-      <c r="T381" s="7" t="s">
+      <c r="T381" t="s">
         <v>306</v>
       </c>
     </row>
@@ -24327,10 +24311,10 @@
       <c r="R382">
         <v>82</v>
       </c>
-      <c r="S382" s="7" t="s">
+      <c r="S382" t="s">
         <v>27</v>
       </c>
-      <c r="T382" s="7" t="s">
+      <c r="T382" t="s">
         <v>307</v>
       </c>
     </row>
@@ -24383,10 +24367,10 @@
       <c r="R383">
         <v>82</v>
       </c>
-      <c r="S383" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T383" s="7" t="s">
+      <c r="S383" t="s">
+        <v>12</v>
+      </c>
+      <c r="T383" t="s">
         <v>308</v>
       </c>
     </row>
@@ -24439,10 +24423,10 @@
       <c r="R384">
         <v>82</v>
       </c>
-      <c r="S384" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T384" s="7" t="s">
+      <c r="S384" t="s">
+        <v>12</v>
+      </c>
+      <c r="T384" t="s">
         <v>309</v>
       </c>
     </row>
@@ -24495,10 +24479,10 @@
       <c r="R385">
         <v>82</v>
       </c>
-      <c r="S385" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T385" s="7" t="s">
+      <c r="S385" t="s">
+        <v>12</v>
+      </c>
+      <c r="T385" t="s">
         <v>310</v>
       </c>
     </row>
@@ -24551,10 +24535,10 @@
       <c r="R386">
         <v>82</v>
       </c>
-      <c r="S386" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T386" s="7" t="s">
+      <c r="S386" t="s">
+        <v>12</v>
+      </c>
+      <c r="T386" t="s">
         <v>311</v>
       </c>
     </row>
@@ -24607,10 +24591,10 @@
       <c r="R387">
         <v>82</v>
       </c>
-      <c r="S387" s="7" t="s">
+      <c r="S387" t="s">
         <v>27</v>
       </c>
-      <c r="T387" s="7" t="s">
+      <c r="T387" t="s">
         <v>312</v>
       </c>
     </row>
@@ -24663,10 +24647,10 @@
       <c r="R388">
         <v>82</v>
       </c>
-      <c r="S388" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T388" s="7" t="s">
+      <c r="S388" t="s">
+        <v>12</v>
+      </c>
+      <c r="T388" t="s">
         <v>313</v>
       </c>
     </row>
@@ -24719,10 +24703,10 @@
       <c r="R389">
         <v>82</v>
       </c>
-      <c r="S389" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T389" s="7" t="s">
+      <c r="S389" t="s">
+        <v>12</v>
+      </c>
+      <c r="T389" t="s">
         <v>314</v>
       </c>
     </row>
@@ -24775,10 +24759,10 @@
       <c r="R390">
         <v>82</v>
       </c>
-      <c r="S390" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T390" s="7" t="s">
+      <c r="S390" t="s">
+        <v>12</v>
+      </c>
+      <c r="T390" t="s">
         <v>315</v>
       </c>
     </row>
@@ -24831,10 +24815,10 @@
       <c r="R391">
         <v>82</v>
       </c>
-      <c r="S391" s="7" t="s">
+      <c r="S391" t="s">
         <v>33</v>
       </c>
-      <c r="T391" s="7" t="s">
+      <c r="T391" t="s">
         <v>316</v>
       </c>
     </row>
@@ -24887,10 +24871,10 @@
       <c r="R392">
         <v>82</v>
       </c>
-      <c r="S392" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T392" s="7" t="s">
+      <c r="S392" t="s">
+        <v>12</v>
+      </c>
+      <c r="T392" t="s">
         <v>317</v>
       </c>
     </row>
@@ -24943,10 +24927,10 @@
       <c r="R393">
         <v>82</v>
       </c>
-      <c r="S393" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T393" s="7" t="s">
+      <c r="S393" t="s">
+        <v>12</v>
+      </c>
+      <c r="T393" t="s">
         <v>318</v>
       </c>
     </row>
@@ -24999,10 +24983,10 @@
       <c r="R394">
         <v>82</v>
       </c>
-      <c r="S394" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T394" s="7" t="s">
+      <c r="S394" t="s">
+        <v>12</v>
+      </c>
+      <c r="T394" t="s">
         <v>319</v>
       </c>
     </row>
@@ -25273,31 +25257,31 @@
       <c r="D8" s="1" t="str">
         <v>nbr.val</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>392</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>392</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>392</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>392</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>392</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>392</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="7">
         <v>392</v>
       </c>
-      <c r="L8" s="8" t="b">
+      <c r="L8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="8" t="b">
+      <c r="M8" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25305,31 +25289,31 @@
       <c r="D9" s="1" t="str">
         <v>nbr.null</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>0</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>0</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>0</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>0</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>0</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="7">
         <v>0</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="7">
         <v>0</v>
       </c>
-      <c r="L9" s="8" t="b">
+      <c r="L9" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M9" s="8" t="b">
+      <c r="M9" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25337,31 +25321,31 @@
       <c r="D10" s="1" t="str">
         <v>nbr.na</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>0</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>0</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>0</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>0</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <v>0</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="7">
         <v>0</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="7">
         <v>0</v>
       </c>
-      <c r="L10" s="8" t="b">
+      <c r="L10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M10" s="8" t="b">
+      <c r="M10" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25369,31 +25353,31 @@
       <c r="D11" s="1" t="str">
         <v>min</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>9</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>3</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>68</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>46</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>1613</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <v>8</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <v>70</v>
       </c>
-      <c r="L11" s="8" t="b">
+      <c r="L11" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M11" s="8" t="b">
+      <c r="M11" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25401,31 +25385,31 @@
       <c r="D12" s="1" t="str">
         <v>max</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>46.6</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>8</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>455</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>230</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>5140</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="7">
         <v>24.8</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="7">
         <v>82</v>
       </c>
-      <c r="L12" s="8" t="b">
+      <c r="L12" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M12" s="8" t="b">
+      <c r="M12" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25433,31 +25417,31 @@
       <c r="D13" s="1" t="str">
         <v>range</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>37.6</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>387</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>184</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>3527</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="7">
         <v>16.8</v>
       </c>
-      <c r="K13" s="8">
-        <v>12</v>
-      </c>
-      <c r="L13" s="8" t="b">
+      <c r="K13" s="7">
+        <v>12</v>
+      </c>
+      <c r="L13" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M13" s="8" t="b">
+      <c r="M13" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25465,31 +25449,31 @@
       <c r="D14" s="1" t="str">
         <v>sum</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>9190.7999999999993</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>2145</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>76209.5</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>40952</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>1167213</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="7">
         <v>6092.2</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="7">
         <v>29784</v>
       </c>
-      <c r="L14" s="8" t="b">
+      <c r="L14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M14" s="8" t="b">
+      <c r="M14" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25497,31 +25481,31 @@
       <c r="D15" s="1" t="str">
         <v>median</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>22.75</v>
       </c>
-      <c r="F15" s="8">
-        <v>4</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="F15" s="7">
+        <v>4</v>
+      </c>
+      <c r="G15" s="7">
         <v>151</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <v>93.5</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <v>2803.5</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <v>15.5</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="7">
         <v>76</v>
       </c>
-      <c r="L15" s="8" t="b">
+      <c r="L15" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M15" s="8" t="b">
+      <c r="M15" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25529,31 +25513,31 @@
       <c r="D16" s="1" t="str">
         <v>mean</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>23.445918367346938</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>5.4719387755102042</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>194.41198979591837</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>104.46938775510205</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>2977.5841836734694</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>15.541326530612245</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <v>75.979591836734699</v>
       </c>
-      <c r="L16" s="8" t="b">
+      <c r="L16" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M16" s="8" t="b">
+      <c r="M16" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25561,31 +25545,31 @@
       <c r="D17" s="1" t="str">
         <v>SE.mean</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>0.39421240864047785</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>8.6155064393448194E-2</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>5.2853203410355762</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>1.9440971574456398</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>42.901307868827359</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>0.13934368050358173</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="8">
         <v>0.1860567921477555</v>
       </c>
-      <c r="L17" s="8" t="b">
+      <c r="L17" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="8" t="b">
+      <c r="M17" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25593,31 +25577,31 @@
       <c r="D18" s="1" t="str">
         <v>CI.mean.0.95</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>0.77504117957383289</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>0.16938513671865496</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>10.391202361358578</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>3.8221915928754209</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>84.346102575985654</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>0.27395659836306357</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="8">
         <v>0.36579689652902825</v>
       </c>
-      <c r="L18" s="8" t="b">
+      <c r="L18" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M18" s="8" t="b">
+      <c r="M18" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25625,31 +25609,31 @@
       <c r="D19" s="1" t="str">
         <v>var</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>60.918141865441832</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>2.9096964872905682</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>10950.367554086852</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>1481.5693929745812</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <v>721484.70900751604</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="8">
         <v>7.6113312281434311</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="8">
         <v>13.569914922490735</v>
       </c>
-      <c r="L19" s="8" t="b">
+      <c r="L19" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M19" s="8" t="b">
+      <c r="M19" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25657,31 +25641,31 @@
       <c r="D20" s="1" t="str">
         <v>std.dev</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <v>7.8050074865717987</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>1.7057832474527848</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>104.64400390890465</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>38.491159932828488</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <v>849.40256004294929</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="8">
         <v>2.7588641191880821</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="8">
         <v>3.6837365435778295</v>
       </c>
-      <c r="L20" s="8" t="b">
+      <c r="L20" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M20" s="8" t="b">
+      <c r="M20" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25689,31 +25673,31 @@
       <c r="D21" s="1" t="str">
         <v>coef.var</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <v>0.33289408264091758</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>0.31173288251817788</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>0.53825900356636147</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>0.36844439083973352</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <v>0.28526567433436412</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="8">
         <v>0.17751793025864682</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="8">
         <v>4.8483236807766221E-2</v>
       </c>
-      <c r="L21" s="8" t="b">
+      <c r="L21" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M21" s="8" t="b">
+      <c r="M21" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25721,31 +25705,31 @@
       <c r="D22" s="1" t="str">
         <v>skewness</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>0.45360011677088963</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>0.50422726242069404</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>0.69630831559027684</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <v>1.0790190597922649</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="8">
         <v>0.51561601570162785</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="8">
         <v>0.28935918826910989</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="8">
         <v>1.9537880117715851E-2</v>
       </c>
-      <c r="L22" s="8" t="b">
+      <c r="L22" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M22" s="8" t="b">
+      <c r="M22" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25753,31 +25737,31 @@
       <c r="D23" s="1" t="str">
         <v>skew.2SE</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <v>1.8401924779803867</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>2.0455797544864107</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>2.8248258263822659</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <v>4.3774299961878302</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="8">
         <v>2.0917823398612607</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="8">
         <v>1.1738899131639264</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="8">
         <v>7.9262457611895001E-2</v>
       </c>
-      <c r="L23" s="8" t="b">
+      <c r="L23" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M23" s="8" t="b">
+      <c r="M23" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25785,31 +25769,31 @@
       <c r="D24" s="1" t="str">
         <v>kurtosis</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="8">
         <v>-0.53731554333408527</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="8">
         <v>-1.4038700128669117</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>-0.79498525582101731</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>0.65410689957850154</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="8">
         <v>-0.82537878230248118</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="8">
         <v>0.40587669121449821</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="8">
         <v>-1.1772112361408742</v>
       </c>
-      <c r="L24" s="8" t="b">
+      <c r="L24" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M24" s="8" t="b">
+      <c r="M24" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25817,31 +25801,31 @@
       <c r="D25" s="1" t="str">
         <v>kurt.2SE</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="8">
         <v>-1.0926344813616564</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="8">
         <v>-2.8547783559171687</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="8">
         <v>-1.6166074357243678</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <v>1.3301304267903156</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="8">
         <v>-1.6784128598477079</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="8">
         <v>0.82535276245712519</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="8">
         <v>-2.3938663312669948</v>
       </c>
-      <c r="L25" s="8" t="b">
+      <c r="L25" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M25" s="8" t="b">
+      <c r="M25" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25849,31 +25833,31 @@
       <c r="D26" s="1" t="str">
         <v>normtest.W</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="8">
         <v>0.96716962156641939</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="8">
         <v>0.75065968159361696</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="8">
         <v>0.88183594112678176</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="8">
         <v>0.90409748782389998</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="8">
         <v>0.94146607393242454</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="8">
         <v>0.99186713639922131</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="8">
         <v>0.9469665939784816</v>
       </c>
-      <c r="L26" s="8" t="b">
+      <c r="L26" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M26" s="8" t="b">
+      <c r="M26" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25881,43 +25865,43 @@
       <c r="D27" s="1" t="str">
         <v>normtest.p</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <v>1.0494405382804953E-7</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <v>6.8802413270666092E-24</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="8">
         <v>8.9836361331958086E-17</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <v>5.0220689766168479E-15</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="8">
         <v>2.6016854178190008E-11</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="8">
         <v>3.0528860864288031E-2</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="8">
         <v>1.2226167114074609E-10</v>
       </c>
-      <c r="L27" s="8" t="b">
+      <c r="L27" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="M27" s="8" t="b">
+      <c r="M27" s="7" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:D3">
-    <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="#">
-      <formula>LEFT(B2,LEN("#"))="#"</formula>
+  <conditionalFormatting sqref="B6:B7">
+    <cfRule type="beginsWith" dxfId="5" priority="1" operator="beginsWith" text="#">
+      <formula>LEFT(B6,LEN("#"))="#"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B7">
-    <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="#">
-      <formula>LEFT(B6,LEN("#"))="#"</formula>
+  <conditionalFormatting sqref="B2:D3">
+    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="#">
+      <formula>LEFT(B2,LEN("#"))="#"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25959,10 +25943,10 @@
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
@@ -25984,7 +25968,7 @@
       <c r="B21" t="s">
         <v>332</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>343</v>
       </c>
     </row>
@@ -25992,7 +25976,7 @@
       <c r="B22" t="s">
         <v>333</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>344</v>
       </c>
     </row>
@@ -26000,7 +25984,7 @@
       <c r="B23" t="s">
         <v>334</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>345</v>
       </c>
     </row>
@@ -26037,7 +26021,7 @@
       </c>
     </row>
     <row r="31" spans="2:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>349</v>
       </c>
       <c r="D31" t="str" cm="1">
@@ -26046,7 +26030,7 @@
       </c>
     </row>
     <row r="34" spans="2:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>350</v>
       </c>
       <c r="D34" t="str" cm="1">
@@ -26055,7 +26039,7 @@
       </c>
     </row>
     <row r="37" spans="2:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>351</v>
       </c>
       <c r="D37" t="str" cm="1">
@@ -26067,14 +26051,14 @@
   <mergeCells count="1">
     <mergeCell ref="B18:C18"/>
   </mergeCells>
-  <conditionalFormatting sqref="B2:D3">
-    <cfRule type="beginsWith" dxfId="3" priority="2" operator="beginsWith" text="#">
-      <formula>LEFT(B2,LEN("#"))="#"</formula>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="beginsWith" dxfId="3" priority="1" operator="beginsWith" text="#">
+      <formula>LEFT(B30,LEN("#"))="#"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="#">
-      <formula>LEFT(B30,LEN("#"))="#"</formula>
+  <conditionalFormatting sqref="B2:D3">
+    <cfRule type="beginsWith" dxfId="2" priority="2" operator="beginsWith" text="#">
+      <formula>LEFT(B2,LEN("#"))="#"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26117,10 +26101,10 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="C21" s="11"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
@@ -26275,132 +26259,132 @@
       <c r="B6" t="s">
         <v>372</v>
       </c>
-      <c r="D6" s="16" t="str" cm="1">
-        <f t="array" ref="D6:I11">_xll.RScript.Evaluate("as.data.frame("&amp;B7&amp;")")</f>
+      <c r="D6" s="13" t="str" cm="1">
+        <f t="array" ref="D6:I11">_xll.RScript.Evaluate(B7, "df")</f>
         <v>Index</v>
       </c>
-      <c r="E6" s="16" t="str">
+      <c r="E6" s="13" t="str">
         <v>mpg</v>
       </c>
-      <c r="F6" s="16" t="str">
+      <c r="F6" s="13" t="str">
         <v>cylinders</v>
       </c>
-      <c r="G6" s="16" t="str">
+      <c r="G6" s="13" t="str">
         <v>displacement</v>
       </c>
-      <c r="H6" s="16" t="str">
+      <c r="H6" s="13" t="str">
         <v>horsepower</v>
       </c>
-      <c r="I6" s="16" t="str">
+      <c r="I6" s="13" t="str">
         <v>weight</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="15" t="str" cm="1">
+      <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xll.RScript.Evaluate(B6)</f>
         <v>res</v>
       </c>
-      <c r="D7" s="16" t="str">
+      <c r="D7" s="13" t="str">
         <v>mpg</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>1</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <v>-0.77761750812602248</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="11">
         <v>-0.80512694671045781</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="11">
         <v>-0.77842678389777598</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="11">
         <v>-0.83224421483157551</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D8" s="16" t="str">
+      <c r="D8" s="13" t="str">
         <v>cylinders</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>-0.77761750812602248</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <v>1</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="11">
         <v>0.95082330082778255</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="11">
         <v>0.84298335691865633</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>0.89752734034081705</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D9" s="16" t="str">
+      <c r="D9" s="13" t="str">
         <v>displacement</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>-0.80512694671045781</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="11">
         <v>0.95082330082778255</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="12">
         <v>1</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="11">
         <v>0.89725700184346902</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="11">
         <v>0.93299440408901058</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D10" s="16" t="str">
+      <c r="D10" s="13" t="str">
         <v>horsepower</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>-0.77842678389777598</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="11">
         <v>0.84298335691865633</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="11">
         <v>0.89725700184346902</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="12">
         <v>1</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="11">
         <v>0.8645377375741442</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D11" s="16" t="str">
+      <c r="D11" s="13" t="str">
         <v>weight</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11">
         <v>-0.83224421483157551</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="11">
         <v>0.89752734034081705</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="11">
         <v>0.93299440408901058</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="11">
         <v>0.8645377375741442</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>374</v>
       </c>
       <c r="D14" t="str" cm="1">
